--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9D06C6D-A139-40EB-9D91-1AE34552D4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60C2C938-7543-44AB-AC9C-65B3B5CD5909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{18C5D629-221A-4EB6-9E09-41C72B8C3C53}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DC07F70D-D470-4003-BD3C-1E04A50F3E7B}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3224,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CC4CA7-52D8-4505-A893-ACB618913350}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C75B869-4659-4494-BAA2-428177417A99}">
   <dimension ref="B9:T336"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19370,7 +19370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE2E379D-4D16-4CC0-A6AD-7193717933A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ACADFE3-DC6B-4196-B4F0-987C1B40285F}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41810,7 +41810,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L486">
-        <v>0.16655441184208444</v>
+        <v>0.16655441184208439</v>
       </c>
     </row>
     <row r="487" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60C2C938-7543-44AB-AC9C-65B3B5CD5909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E0E86E-91AA-47DD-B2C3-5DD6E5FA7888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{DC07F70D-D470-4003-BD3C-1E04A50F3E7B}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4F55FFF3-3C44-4DC6-8E86-BB65654EC5F8}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3224,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C75B869-4659-4494-BAA2-428177417A99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312E5D6-5176-4427-BB3C-F5DD7649F977}">
   <dimension ref="B9:T336"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19370,7 +19370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ACADFE3-DC6B-4196-B4F0-987C1B40285F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E6F61B3-CE49-42A3-8BD4-50A9B7E06180}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41064,7 +41064,7 @@
         <v>33</v>
       </c>
       <c r="L464">
-        <v>0.21517651100570445</v>
+        <v>0.2151765110057044</v>
       </c>
     </row>
     <row r="465" spans="2:12" x14ac:dyDescent="0.45">
@@ -41810,7 +41810,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L486">
-        <v>0.16655441184208439</v>
+        <v>0.16655441184208447</v>
       </c>
     </row>
     <row r="487" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E0E86E-91AA-47DD-B2C3-5DD6E5FA7888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4051C82-8458-4E62-86D9-46101EB01820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{4F55FFF3-3C44-4DC6-8E86-BB65654EC5F8}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{125A4BCB-F318-43E8-861D-601DA5284FFB}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3224,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D312E5D6-5176-4427-BB3C-F5DD7649F977}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F298EEA5-09F4-4EB7-883D-A29365A29361}">
   <dimension ref="B9:T336"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19370,7 +19370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E6F61B3-CE49-42A3-8BD4-50A9B7E06180}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31CC431-F40E-40C7-8BC8-CCCA9AC887F6}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41064,7 +41064,7 @@
         <v>33</v>
       </c>
       <c r="L464">
-        <v>0.2151765110057044</v>
+        <v>0.21517651100570445</v>
       </c>
     </row>
     <row r="465" spans="2:12" x14ac:dyDescent="0.45">
@@ -41810,7 +41810,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L486">
-        <v>0.16655441184208447</v>
+        <v>0.16655441184208444</v>
       </c>
     </row>
     <row r="487" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4051C82-8458-4E62-86D9-46101EB01820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C3FAA0-FE0D-41FE-B2E5-368B296E1518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{125A4BCB-F318-43E8-861D-601DA5284FFB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D94937E2-43A2-4B2B-BA65-3A853C3DD0F6}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3224,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F298EEA5-09F4-4EB7-883D-A29365A29361}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE92778-8859-408B-8C13-5EB2CE4DE553}">
   <dimension ref="B9:T336"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19370,7 +19370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31CC431-F40E-40C7-8BC8-CCCA9AC887F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2108AE-CBE9-480A-8062-857C4D4F915C}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41064,7 +41064,7 @@
         <v>33</v>
       </c>
       <c r="L464">
-        <v>0.21517651100570445</v>
+        <v>0.2151765110057044</v>
       </c>
     </row>
     <row r="465" spans="2:12" x14ac:dyDescent="0.45">
@@ -41810,7 +41810,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L486">
-        <v>0.16655441184208444</v>
+        <v>0.16655441184208447</v>
       </c>
     </row>
     <row r="487" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C9C3FAA0-FE0D-41FE-B2E5-368B296E1518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51766246-BC37-405B-86E3-59517F02C84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D94937E2-43A2-4B2B-BA65-3A853C3DD0F6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AB6FF4B1-55D8-4842-AF3A-8BA69505E380}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -1107,7 +1107,7 @@
     <t>ep_solar_thermal_ITA</t>
   </si>
   <si>
-    <t>ep_windoff_wind_c_wof-ITA</t>
+    <t>ep_windoff_wind_ITA</t>
   </si>
   <si>
     <t>windoff</t>
@@ -1125,7 +1125,7 @@
     <t>elc_won-ITA</t>
   </si>
   <si>
-    <t>ep_windon_wind_c_won-ITA</t>
+    <t>ep_windon_wind_ITA</t>
   </si>
   <si>
     <t>~fi_process</t>
@@ -3224,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DE92778-8859-408B-8C13-5EB2CE4DE553}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E79A98DA-0D03-4253-9EEE-4B04469EB76B}">
   <dimension ref="B9:T336"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19370,7 +19370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2108AE-CBE9-480A-8062-857C4D4F915C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9BA3EA-5ACA-4597-AF92-F957E0CF8F23}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41064,7 +41064,7 @@
         <v>33</v>
       </c>
       <c r="L464">
-        <v>0.2151765110057044</v>
+        <v>0.21912812891333874</v>
       </c>
     </row>
     <row r="465" spans="2:12" x14ac:dyDescent="0.45">
@@ -41099,7 +41099,7 @@
         <v>46</v>
       </c>
       <c r="L465">
-        <v>0.21507650674536258</v>
+        <v>0.21706775707037165</v>
       </c>
     </row>
     <row r="466" spans="2:12" x14ac:dyDescent="0.45">
@@ -41134,7 +41134,7 @@
         <v>45</v>
       </c>
       <c r="L466">
-        <v>0.19832534665850599</v>
+        <v>0.20181921892918547</v>
       </c>
     </row>
     <row r="467" spans="2:12" x14ac:dyDescent="0.45">
@@ -41169,7 +41169,7 @@
         <v>44</v>
       </c>
       <c r="L467">
-        <v>0.20356134267738368</v>
+        <v>0.20830123832604813</v>
       </c>
     </row>
     <row r="468" spans="2:12" x14ac:dyDescent="0.45">
@@ -41204,7 +41204,7 @@
         <v>43</v>
       </c>
       <c r="L468">
-        <v>0.21929097392436972</v>
+        <v>0.22360997876486408</v>
       </c>
     </row>
     <row r="469" spans="2:12" x14ac:dyDescent="0.45">
@@ -41239,7 +41239,7 @@
         <v>42</v>
       </c>
       <c r="L469">
-        <v>0.20835150539001851</v>
+        <v>0.21284167720871763</v>
       </c>
     </row>
     <row r="470" spans="2:12" x14ac:dyDescent="0.45">
@@ -41274,7 +41274,7 @@
         <v>40</v>
       </c>
       <c r="L470">
-        <v>0.20059098809436526</v>
+        <v>0.2055324235831229</v>
       </c>
     </row>
     <row r="471" spans="2:12" x14ac:dyDescent="0.45">
@@ -41309,7 +41309,7 @@
         <v>39</v>
       </c>
       <c r="L471">
-        <v>0.229397715</v>
+        <v>0.22990287162581269</v>
       </c>
     </row>
     <row r="472" spans="2:12" x14ac:dyDescent="0.45">
@@ -41344,7 +41344,7 @@
         <v>37</v>
       </c>
       <c r="L472">
-        <v>0.227790834</v>
+        <v>0.22779083409784781</v>
       </c>
     </row>
     <row r="473" spans="2:12" x14ac:dyDescent="0.45">
@@ -41379,7 +41379,7 @@
         <v>35</v>
       </c>
       <c r="L473">
-        <v>0.20786610901459859</v>
+        <v>0.21336851641293197</v>
       </c>
     </row>
     <row r="474" spans="2:12" x14ac:dyDescent="0.45">
@@ -41414,7 +41414,7 @@
         <v>34</v>
       </c>
       <c r="L474">
-        <v>0.21057682999999999</v>
+        <v>0.21831799184116799</v>
       </c>
     </row>
     <row r="475" spans="2:12" x14ac:dyDescent="0.45">
@@ -41449,7 +41449,7 @@
         <v>33</v>
       </c>
       <c r="L475">
-        <v>0.22917167631756757</v>
+        <v>0.23127337043893853</v>
       </c>
     </row>
     <row r="476" spans="2:12" x14ac:dyDescent="0.45">
@@ -41484,7 +41484,7 @@
         <v>32</v>
       </c>
       <c r="L476">
-        <v>0.21148318002343752</v>
+        <v>0.21488465282287167</v>
       </c>
     </row>
     <row r="477" spans="2:12" x14ac:dyDescent="0.45">
@@ -41519,7 +41519,7 @@
         <v>31</v>
       </c>
       <c r="L477">
-        <v>0.2003355556928702</v>
+        <v>0.20831016768126159</v>
       </c>
     </row>
     <row r="478" spans="2:12" x14ac:dyDescent="0.45">
@@ -41554,7 +41554,7 @@
         <v>30</v>
       </c>
       <c r="L478">
-        <v>0.20560763590751446</v>
+        <v>0.21323609886036252</v>
       </c>
     </row>
     <row r="479" spans="2:12" x14ac:dyDescent="0.45">
@@ -41589,7 +41589,7 @@
         <v>30</v>
       </c>
       <c r="L479">
-        <v>0.22487976800000001</v>
+        <v>0.22817316965907841</v>
       </c>
     </row>
     <row r="480" spans="2:12" x14ac:dyDescent="0.45">
@@ -41624,7 +41624,7 @@
         <v>30</v>
       </c>
       <c r="L480">
-        <v>0.20736176066809481</v>
+        <v>0.21657497252407351</v>
       </c>
     </row>
     <row r="481" spans="2:12" x14ac:dyDescent="0.45">
@@ -41659,7 +41659,7 @@
         <v>45</v>
       </c>
       <c r="L481">
-        <v>0.23130788899999996</v>
+        <v>0.23503582548657823</v>
       </c>
     </row>
     <row r="482" spans="2:12" x14ac:dyDescent="0.45">
@@ -41694,7 +41694,7 @@
         <v>41</v>
       </c>
       <c r="L482">
-        <v>0.21995019099999999</v>
+        <v>0.21995019137019761</v>
       </c>
     </row>
     <row r="483" spans="2:12" x14ac:dyDescent="0.45">
@@ -41729,7 +41729,7 @@
         <v>34</v>
       </c>
       <c r="L483">
-        <v>0.22541493300000001</v>
+        <v>0.22897581092516031</v>
       </c>
     </row>
     <row r="484" spans="2:12" x14ac:dyDescent="0.45">
@@ -41764,7 +41764,7 @@
         <v>30</v>
       </c>
       <c r="L484">
-        <v>0.227189479</v>
+        <v>0.22759581063818146</v>
       </c>
     </row>
     <row r="485" spans="2:12" x14ac:dyDescent="0.45">
@@ -41787,7 +41787,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L485">
-        <v>0.231993951</v>
+        <v>0.25319260034140117</v>
       </c>
     </row>
     <row r="486" spans="2:12" x14ac:dyDescent="0.45">
@@ -41810,7 +41810,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L486">
-        <v>0.16655441184208447</v>
+        <v>0.21825043948193773</v>
       </c>
     </row>
     <row r="487" spans="2:12" x14ac:dyDescent="0.45">
@@ -41833,7 +41833,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L487">
-        <v>0.152348923</v>
+        <v>0.15234892163100239</v>
       </c>
     </row>
     <row r="488" spans="2:12" x14ac:dyDescent="0.45">
@@ -41856,7 +41856,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L488">
-        <v>0.152348923</v>
+        <v>0.15234892163100239</v>
       </c>
     </row>
     <row r="489" spans="2:12" x14ac:dyDescent="0.45">
@@ -41879,7 +41879,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L489">
-        <v>0.102161191</v>
+        <v>0.15234892163100239</v>
       </c>
     </row>
     <row r="490" spans="2:12" x14ac:dyDescent="0.45">
@@ -41902,7 +41902,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L490">
-        <v>0.152348923</v>
+        <v>0.22190181133099771</v>
       </c>
     </row>
     <row r="491" spans="2:12" x14ac:dyDescent="0.45">
@@ -41925,7 +41925,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L491">
-        <v>0.17150900447368422</v>
+        <v>0.23572151776258343</v>
       </c>
     </row>
     <row r="492" spans="2:12" x14ac:dyDescent="0.45">
@@ -41948,7 +41948,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L492">
-        <v>0.13777541851063829</v>
+        <v>0.19765440310818475</v>
       </c>
     </row>
     <row r="493" spans="2:12" x14ac:dyDescent="0.45">
@@ -41971,7 +41971,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L493">
-        <v>0.17459019660940697</v>
+        <v>0.24498513650408277</v>
       </c>
     </row>
     <row r="494" spans="2:12" x14ac:dyDescent="0.45">
@@ -41994,7 +41994,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L494">
-        <v>0.29201470299999999</v>
+        <v>0.292014702231014</v>
       </c>
     </row>
     <row r="495" spans="2:12" x14ac:dyDescent="0.45">
@@ -42017,7 +42017,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L495">
-        <v>0.17790534255555557</v>
+        <v>0.27218456548796333</v>
       </c>
     </row>
     <row r="496" spans="2:12" x14ac:dyDescent="0.45">
@@ -42040,7 +42040,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L496">
-        <v>0.17133578397256857</v>
+        <v>0.23235784961716674</v>
       </c>
     </row>
     <row r="497" spans="2:12" x14ac:dyDescent="0.45">
@@ -42063,7 +42063,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L497">
-        <v>0.12829636734965033</v>
+        <v>0.17937300343451007</v>
       </c>
     </row>
     <row r="498" spans="2:12" x14ac:dyDescent="0.45">
@@ -42086,7 +42086,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L498">
-        <v>0.1692052287093207</v>
+        <v>0.23504252561933539</v>
       </c>
     </row>
     <row r="499" spans="2:12" x14ac:dyDescent="0.45">
@@ -42109,7 +42109,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L499">
-        <v>0.18129480242538354</v>
+        <v>0.23336238162494113</v>
       </c>
     </row>
     <row r="500" spans="2:12" x14ac:dyDescent="0.45">
@@ -42132,7 +42132,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L500">
-        <v>0.1562900223861004</v>
+        <v>0.20078458232543456</v>
       </c>
     </row>
     <row r="501" spans="2:12" x14ac:dyDescent="0.45">
@@ -42155,7 +42155,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L501">
-        <v>0.14197011712538696</v>
+        <v>0.1761175256342413</v>
       </c>
     </row>
     <row r="502" spans="2:12" x14ac:dyDescent="0.45">
@@ -42178,7 +42178,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L502">
-        <v>0.1736624771920956</v>
+        <v>0.21668806053184619</v>
       </c>
     </row>
     <row r="503" spans="2:12" x14ac:dyDescent="0.45">
@@ -42201,7 +42201,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L503">
-        <v>0.16501702958106171</v>
+        <v>0.20633725223643881</v>
       </c>
     </row>
     <row r="504" spans="2:12" x14ac:dyDescent="0.45">
@@ -42224,7 +42224,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L504">
-        <v>0.19990784586311786</v>
+        <v>0.24761424368343879</v>
       </c>
     </row>
     <row r="505" spans="2:12" x14ac:dyDescent="0.45">
@@ -42247,7 +42247,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L505">
-        <v>0.13110785929213481</v>
+        <v>0.20182865739050115</v>
       </c>
     </row>
     <row r="506" spans="2:12" x14ac:dyDescent="0.45">
@@ -42270,7 +42270,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L506">
-        <v>0.1403115752913327</v>
+        <v>0.1892248131241227</v>
       </c>
     </row>
     <row r="507" spans="2:12" x14ac:dyDescent="0.45">
@@ -42293,7 +42293,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L507">
-        <v>0.215669247875</v>
+        <v>0.24931751577573705</v>
       </c>
     </row>
     <row r="508" spans="2:12" x14ac:dyDescent="0.45">
@@ -42316,7 +42316,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L508">
-        <v>0.13683248341148324</v>
+        <v>0.19179768906089875</v>
       </c>
     </row>
     <row r="509" spans="2:12" x14ac:dyDescent="0.45">
@@ -42339,7 +42339,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L509">
-        <v>0.1733749360321101</v>
+        <v>0.22967643282521613</v>
       </c>
     </row>
     <row r="510" spans="2:12" x14ac:dyDescent="0.45">
@@ -42362,7 +42362,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L510">
-        <v>0.12955001024999999</v>
+        <v>0.17720505082852875</v>
       </c>
     </row>
     <row r="511" spans="2:12" x14ac:dyDescent="0.45">
@@ -42385,7 +42385,7 @@
         <v>0.33122999999999997</v>
       </c>
       <c r="L511">
-        <v>0.15001023312711864</v>
+        <v>0.19089931079468306</v>
       </c>
     </row>
     <row r="512" spans="2:12" x14ac:dyDescent="0.45">
@@ -42408,7 +42408,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L512">
-        <v>0.20422734272239754</v>
+        <v>0.25535065154266207</v>
       </c>
     </row>
     <row r="513" spans="2:12" x14ac:dyDescent="0.45">
@@ -42431,7 +42431,7 @@
         <v>0.33123000000000008</v>
       </c>
       <c r="L513">
-        <v>0.24369812832729809</v>
+        <v>0.31737175129195183</v>
       </c>
     </row>
     <row r="514" spans="2:12" x14ac:dyDescent="0.45">
@@ -42454,7 +42454,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L514">
-        <v>0.14780523517968749</v>
+        <v>0.21883762009890731</v>
       </c>
     </row>
     <row r="515" spans="2:12" x14ac:dyDescent="0.45">
@@ -42477,7 +42477,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L515">
-        <v>0.221901813</v>
+        <v>0.25491555436873869</v>
       </c>
     </row>
     <row r="516" spans="2:12" x14ac:dyDescent="0.45">
@@ -42500,7 +42500,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L516">
-        <v>0.102161191</v>
+        <v>0.22190181133099773</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{51766246-BC37-405B-86E3-59517F02C84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72BB2EAF-9576-47BB-A5FF-8F928CD03926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AB6FF4B1-55D8-4842-AF3A-8BA69505E380}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{81D5AC7B-673E-4CDB-AF6A-E734C33FC328}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3224,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E79A98DA-0D03-4253-9EEE-4B04469EB76B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D09E71-B218-4FD8-96CA-518827AEEF91}">
   <dimension ref="B9:T336"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19370,7 +19370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9BA3EA-5ACA-4597-AF92-F957E0CF8F23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019B52E1-1C36-4619-8790-318C88A7A1CB}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41064,7 +41064,7 @@
         <v>33</v>
       </c>
       <c r="L464">
-        <v>0.21912812891333874</v>
+        <v>0.21912812891333872</v>
       </c>
     </row>
     <row r="465" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72BB2EAF-9576-47BB-A5FF-8F928CD03926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94A0ABC2-CE42-421A-AAA6-9C6E0919341C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{81D5AC7B-673E-4CDB-AF6A-E734C33FC328}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9965E230-49DE-4687-A289-8D4747BB86FC}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3224,7 +3224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D09E71-B218-4FD8-96CA-518827AEEF91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D06663E0-1EFA-4B31-8714-6DEAF6A5FC0A}">
   <dimension ref="B9:T336"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -19370,7 +19370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019B52E1-1C36-4619-8790-318C88A7A1CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8948DEA2-4A67-4926-97A6-5FBAF02A4D86}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41064,7 +41064,7 @@
         <v>33</v>
       </c>
       <c r="L464">
-        <v>0.21912812891333872</v>
+        <v>0.21912812891333866</v>
       </c>
     </row>
     <row r="465" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28BCA3CA-442D-4CDD-89DD-AC13259A2E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95E3D69D-9858-4BFC-9F4E-D4FB4BE46DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5D0F5BE2-C1FC-4788-B8FC-98CD7AFBF4FE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{34D4C606-5817-4BE6-BDA0-A07B5402F2C4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2624,7 +2624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9C2A80F-4347-41D1-8260-7C3CE9C413CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9398CFD-10D2-4B49-9678-249B1984F90F}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11280,7 +11280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB12E4AB-4D27-4E5F-8D2F-B8F0142D5494}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2FC0B9-BD12-4C5D-9ABD-F544C3419AA4}">
   <dimension ref="B9:T362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25946,7 +25946,7 @@
         <v>33</v>
       </c>
       <c r="L310">
-        <v>0.21912812891333874</v>
+        <v>0.21912812891333872</v>
       </c>
     </row>
     <row r="311" spans="2:12" x14ac:dyDescent="0.45">
@@ -26692,7 +26692,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L332">
-        <v>0.21825043948193773</v>
+        <v>0.2182504394819377</v>
       </c>
     </row>
     <row r="333" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95E3D69D-9858-4BFC-9F4E-D4FB4BE46DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F108C24C-7D65-4AC8-BFB2-E191EB1E4679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{34D4C606-5817-4BE6-BDA0-A07B5402F2C4}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9C22F052-05C5-4E21-8FE4-0D7575E8A6FD}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2624,7 +2624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9398CFD-10D2-4B49-9678-249B1984F90F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF4D1D26-975C-44D5-93F9-D46EB35553F4}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2703,19 +2703,19 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.18317520000000001</v>
+        <v>0.12764790000000001</v>
       </c>
       <c r="F11">
-        <v>2757</v>
+        <v>3144</v>
       </c>
       <c r="G11">
-        <v>39.200000000000003</v>
+        <v>43.8</v>
       </c>
       <c r="H11">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="I11">
-        <v>0.63080000000000003</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J11" t="s">
         <v>23</v>
@@ -2759,19 +2759,19 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.18317520000000001</v>
+        <v>0.12764790000000001</v>
       </c>
       <c r="F12">
-        <v>2757</v>
+        <v>3144</v>
       </c>
       <c r="G12">
-        <v>39.200000000000003</v>
+        <v>43.8</v>
       </c>
       <c r="H12">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="I12">
-        <v>0.63080000000000003</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J12" t="s">
         <v>24</v>
@@ -2815,19 +2815,19 @@
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0.18317520000000001</v>
+        <v>0.12764790000000001</v>
       </c>
       <c r="F13">
-        <v>2757</v>
+        <v>3144</v>
       </c>
       <c r="G13">
-        <v>39.200000000000003</v>
+        <v>43.8</v>
       </c>
       <c r="H13">
-        <v>3.35</v>
+        <v>3.94</v>
       </c>
       <c r="I13">
-        <v>0.63080000000000003</v>
+        <v>0.59565000000000001</v>
       </c>
       <c r="J13" t="s">
         <v>25</v>
@@ -2871,19 +2871,19 @@
         <v>14</v>
       </c>
       <c r="E14">
-        <v>0.13765950000000002</v>
+        <v>8.7830160000000032E-2</v>
       </c>
       <c r="F14">
-        <v>3144</v>
+        <v>3583</v>
       </c>
       <c r="G14">
-        <v>43.8</v>
+        <v>49</v>
       </c>
       <c r="H14">
-        <v>3.94</v>
+        <v>4.59</v>
       </c>
       <c r="I14">
-        <v>0.59565000000000001</v>
+        <v>0.5605</v>
       </c>
       <c r="J14" t="s">
         <v>26</v>
@@ -2927,7 +2927,7 @@
         <v>14</v>
       </c>
       <c r="E15">
-        <v>0.11272320000000002</v>
+        <v>9.581472000000002E-2</v>
       </c>
       <c r="F15">
         <v>3583</v>
@@ -2983,7 +2983,7 @@
         <v>14</v>
       </c>
       <c r="E16">
-        <v>0.30649709999999997</v>
+        <v>0.260522535</v>
       </c>
       <c r="F16">
         <v>1967</v>
@@ -3039,7 +3039,7 @@
         <v>14</v>
       </c>
       <c r="E17">
-        <v>0.30649709999999997</v>
+        <v>0.260522535</v>
       </c>
       <c r="F17">
         <v>1967</v>
@@ -3095,7 +3095,7 @@
         <v>14</v>
       </c>
       <c r="E18">
-        <v>0.30649709999999997</v>
+        <v>0.260522535</v>
       </c>
       <c r="F18">
         <v>1967</v>
@@ -3151,7 +3151,7 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>0.33007379999999992</v>
+        <v>0.28056272999999998</v>
       </c>
       <c r="F19">
         <v>1967</v>
@@ -3207,7 +3207,7 @@
         <v>14</v>
       </c>
       <c r="E20">
-        <v>0.33007379999999992</v>
+        <v>0.28056272999999998</v>
       </c>
       <c r="F20">
         <v>1967</v>
@@ -3263,7 +3263,7 @@
         <v>14</v>
       </c>
       <c r="E21">
-        <v>0.33007379999999992</v>
+        <v>0.28056272999999998</v>
       </c>
       <c r="F21">
         <v>1967</v>
@@ -3319,7 +3319,7 @@
         <v>14</v>
       </c>
       <c r="E22">
-        <v>0.49118125000000001</v>
+        <v>0.41750406250000005</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -3375,7 +3375,7 @@
         <v>14</v>
       </c>
       <c r="E23">
-        <v>0.52272499999999988</v>
+        <v>0.44431624999999997</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -3431,7 +3431,7 @@
         <v>14</v>
       </c>
       <c r="E24">
-        <v>0.450625</v>
+        <v>0.38303124999999993</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -3487,7 +3487,7 @@
         <v>14</v>
       </c>
       <c r="E25">
-        <v>0.52272499999999988</v>
+        <v>0.44431624999999997</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -3543,7 +3543,7 @@
         <v>14</v>
       </c>
       <c r="E26">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -3599,7 +3599,7 @@
         <v>14</v>
       </c>
       <c r="E27">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -3655,7 +3655,7 @@
         <v>14</v>
       </c>
       <c r="E28">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -3711,7 +3711,7 @@
         <v>14</v>
       </c>
       <c r="E29">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -3767,7 +3767,7 @@
         <v>14</v>
       </c>
       <c r="E30">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -3823,7 +3823,7 @@
         <v>14</v>
       </c>
       <c r="E31">
-        <v>0.450625</v>
+        <v>0.38303124999999993</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -3879,7 +3879,7 @@
         <v>14</v>
       </c>
       <c r="E32">
-        <v>0.47315625000000006</v>
+        <v>0.40218281250000004</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -3935,7 +3935,7 @@
         <v>14</v>
       </c>
       <c r="E33">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -3991,7 +3991,7 @@
         <v>14</v>
       </c>
       <c r="E34">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -4047,7 +4047,7 @@
         <v>14</v>
       </c>
       <c r="E35">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -4103,7 +4103,7 @@
         <v>14</v>
       </c>
       <c r="E36">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -4159,7 +4159,7 @@
         <v>14</v>
       </c>
       <c r="E37">
-        <v>0.46865000000000007</v>
+        <v>0.3983525</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -4215,7 +4215,7 @@
         <v>14</v>
       </c>
       <c r="E38">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -4271,7 +4271,7 @@
         <v>14</v>
       </c>
       <c r="E39">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -4327,7 +4327,7 @@
         <v>14</v>
       </c>
       <c r="E40">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -4383,7 +4383,7 @@
         <v>14</v>
       </c>
       <c r="E41">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -4439,7 +4439,7 @@
         <v>14</v>
       </c>
       <c r="E42">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -4495,7 +4495,7 @@
         <v>14</v>
       </c>
       <c r="E43">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -4551,7 +4551,7 @@
         <v>14</v>
       </c>
       <c r="E44">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -4607,7 +4607,7 @@
         <v>14</v>
       </c>
       <c r="E45">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -4663,7 +4663,7 @@
         <v>14</v>
       </c>
       <c r="E46">
-        <v>0.47315625000000006</v>
+        <v>0.40218281250000004</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -4719,7 +4719,7 @@
         <v>14</v>
       </c>
       <c r="E47">
-        <v>0.47315625000000006</v>
+        <v>0.40218281250000004</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -4775,7 +4775,7 @@
         <v>14</v>
       </c>
       <c r="E48">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -4831,7 +4831,7 @@
         <v>14</v>
       </c>
       <c r="E49">
-        <v>0.54075000000000006</v>
+        <v>0.45963749999999998</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -4887,7 +4887,7 @@
         <v>14</v>
       </c>
       <c r="E50">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -4943,7 +4943,7 @@
         <v>14</v>
       </c>
       <c r="E51">
-        <v>0.450625</v>
+        <v>0.38303124999999993</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -4999,7 +4999,7 @@
         <v>14</v>
       </c>
       <c r="E52">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -5055,7 +5055,7 @@
         <v>14</v>
       </c>
       <c r="E53">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -5111,7 +5111,7 @@
         <v>14</v>
       </c>
       <c r="E54">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -5167,7 +5167,7 @@
         <v>14</v>
       </c>
       <c r="E55">
-        <v>0.47315625000000006</v>
+        <v>0.40218281249999999</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -5223,7 +5223,7 @@
         <v>14</v>
       </c>
       <c r="E56">
-        <v>0.47315625000000006</v>
+        <v>0.40218281249999999</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -5279,7 +5279,7 @@
         <v>14</v>
       </c>
       <c r="E57">
-        <v>0.450625</v>
+        <v>0.38303124999999993</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -5335,7 +5335,7 @@
         <v>14</v>
       </c>
       <c r="E58">
-        <v>0.450625</v>
+        <v>0.38303124999999993</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -5391,7 +5391,7 @@
         <v>14</v>
       </c>
       <c r="E59">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -5447,7 +5447,7 @@
         <v>14</v>
       </c>
       <c r="E60">
-        <v>0.4911812499999999</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -5503,7 +5503,7 @@
         <v>14</v>
       </c>
       <c r="E61">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -5559,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="E62">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -5615,7 +5615,7 @@
         <v>14</v>
       </c>
       <c r="E63">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -5671,7 +5671,7 @@
         <v>14</v>
       </c>
       <c r="E64">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -5727,7 +5727,7 @@
         <v>14</v>
       </c>
       <c r="E65">
-        <v>0.40556249999999999</v>
+        <v>0.34472812500000005</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -5783,7 +5783,7 @@
         <v>14</v>
       </c>
       <c r="E66">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -5839,7 +5839,7 @@
         <v>14</v>
       </c>
       <c r="E67">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -5895,7 +5895,7 @@
         <v>14</v>
       </c>
       <c r="E68">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -5951,7 +5951,7 @@
         <v>14</v>
       </c>
       <c r="E69">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -6007,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="E70">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -6063,7 +6063,7 @@
         <v>14</v>
       </c>
       <c r="E71">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -6119,7 +6119,7 @@
         <v>14</v>
       </c>
       <c r="E72">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -6175,7 +6175,7 @@
         <v>14</v>
       </c>
       <c r="E73">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -6231,7 +6231,7 @@
         <v>14</v>
       </c>
       <c r="E74">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -6287,7 +6287,7 @@
         <v>14</v>
       </c>
       <c r="E75">
-        <v>0.52272499999999988</v>
+        <v>0.44431624999999997</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -6343,7 +6343,7 @@
         <v>14</v>
       </c>
       <c r="E76">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -6399,7 +6399,7 @@
         <v>14</v>
       </c>
       <c r="E77">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -6455,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="E78">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -6511,7 +6511,7 @@
         <v>14</v>
       </c>
       <c r="E79">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -6567,7 +6567,7 @@
         <v>14</v>
       </c>
       <c r="E80">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -6623,7 +6623,7 @@
         <v>14</v>
       </c>
       <c r="E81">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -6679,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -6735,7 +6735,7 @@
         <v>14</v>
       </c>
       <c r="E83">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -6791,7 +6791,7 @@
         <v>14</v>
       </c>
       <c r="E84">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -6847,7 +6847,7 @@
         <v>14</v>
       </c>
       <c r="E85">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -6903,7 +6903,7 @@
         <v>14</v>
       </c>
       <c r="E86">
-        <v>0.52272499999999988</v>
+        <v>0.44431624999999997</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -6959,7 +6959,7 @@
         <v>14</v>
       </c>
       <c r="E87">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -7015,7 +7015,7 @@
         <v>14</v>
       </c>
       <c r="E88">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -7071,7 +7071,7 @@
         <v>14</v>
       </c>
       <c r="E89">
-        <v>0.52272499999999988</v>
+        <v>0.44431624999999997</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -7127,7 +7127,7 @@
         <v>14</v>
       </c>
       <c r="E90">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -7183,7 +7183,7 @@
         <v>14</v>
       </c>
       <c r="E91">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -7239,7 +7239,7 @@
         <v>14</v>
       </c>
       <c r="E92">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -7295,7 +7295,7 @@
         <v>14</v>
       </c>
       <c r="E93">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -7351,7 +7351,7 @@
         <v>14</v>
       </c>
       <c r="E94">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -7407,7 +7407,7 @@
         <v>14</v>
       </c>
       <c r="E95">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -7463,7 +7463,7 @@
         <v>14</v>
       </c>
       <c r="E96">
-        <v>0.54075000000000006</v>
+        <v>0.45963749999999998</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -7519,7 +7519,7 @@
         <v>14</v>
       </c>
       <c r="E97">
-        <v>0.54075000000000006</v>
+        <v>0.45963749999999998</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -7575,7 +7575,7 @@
         <v>14</v>
       </c>
       <c r="E98">
-        <v>0.54075000000000006</v>
+        <v>0.45963749999999998</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -7631,7 +7631,7 @@
         <v>14</v>
       </c>
       <c r="E99">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -7687,7 +7687,7 @@
         <v>14</v>
       </c>
       <c r="E100">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -7743,7 +7743,7 @@
         <v>14</v>
       </c>
       <c r="E101">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -7799,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="E102">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -7855,7 +7855,7 @@
         <v>14</v>
       </c>
       <c r="E103">
-        <v>0.450625</v>
+        <v>0.38303124999999993</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -7911,7 +7911,7 @@
         <v>14</v>
       </c>
       <c r="E104">
-        <v>0.450625</v>
+        <v>0.38303124999999993</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -7967,7 +7967,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.47315625000000006</v>
+        <v>0.4021828125000001</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -8023,7 +8023,7 @@
         <v>14</v>
       </c>
       <c r="E106">
-        <v>0.450625</v>
+        <v>0.38303124999999993</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -8079,7 +8079,7 @@
         <v>14</v>
       </c>
       <c r="E107">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -8135,7 +8135,7 @@
         <v>14</v>
       </c>
       <c r="E108">
-        <v>0.46865000000000007</v>
+        <v>0.3983525</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -8191,7 +8191,7 @@
         <v>14</v>
       </c>
       <c r="E109">
-        <v>0.46865000000000007</v>
+        <v>0.3983525</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -8247,7 +8247,7 @@
         <v>14</v>
       </c>
       <c r="E110">
-        <v>0.49118125000000001</v>
+        <v>0.41750406249999999</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -8303,7 +8303,7 @@
         <v>14</v>
       </c>
       <c r="E111">
-        <v>0.54075000000000006</v>
+        <v>0.45963749999999998</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -8359,7 +8359,7 @@
         <v>14</v>
       </c>
       <c r="E112">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -8415,7 +8415,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -8471,7 +8471,7 @@
         <v>14</v>
       </c>
       <c r="E114">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -8527,7 +8527,7 @@
         <v>14</v>
       </c>
       <c r="E115">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -8583,7 +8583,7 @@
         <v>14</v>
       </c>
       <c r="E116">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -8639,7 +8639,7 @@
         <v>14</v>
       </c>
       <c r="E117">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -8695,7 +8695,7 @@
         <v>14</v>
       </c>
       <c r="E118">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -8751,7 +8751,7 @@
         <v>14</v>
       </c>
       <c r="E119">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -8807,7 +8807,7 @@
         <v>14</v>
       </c>
       <c r="E120">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -8863,7 +8863,7 @@
         <v>14</v>
       </c>
       <c r="E121">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -8919,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="E122">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -8975,7 +8975,7 @@
         <v>14</v>
       </c>
       <c r="E123">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -9031,7 +9031,7 @@
         <v>14</v>
       </c>
       <c r="E124">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -9087,7 +9087,7 @@
         <v>14</v>
       </c>
       <c r="E125">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -9143,7 +9143,7 @@
         <v>14</v>
       </c>
       <c r="E126">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F126">
         <v>1365</v>
@@ -9199,7 +9199,7 @@
         <v>14</v>
       </c>
       <c r="E127">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F127">
         <v>1365</v>
@@ -9255,7 +9255,7 @@
         <v>14</v>
       </c>
       <c r="E128">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F128">
         <v>1365</v>
@@ -9311,7 +9311,7 @@
         <v>14</v>
       </c>
       <c r="E129">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F129">
         <v>1365</v>
@@ -9367,7 +9367,7 @@
         <v>14</v>
       </c>
       <c r="E130">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F130">
         <v>1365</v>
@@ -9423,7 +9423,7 @@
         <v>14</v>
       </c>
       <c r="E131">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F131">
         <v>1365</v>
@@ -9479,7 +9479,7 @@
         <v>14</v>
       </c>
       <c r="E132">
-        <v>0.50470000000000004</v>
+        <v>0.42899500000000002</v>
       </c>
       <c r="F132">
         <v>1365</v>
@@ -9535,7 +9535,7 @@
         <v>14</v>
       </c>
       <c r="E133">
-        <v>0.29741250000000002</v>
+        <v>0.25280062500000006</v>
       </c>
       <c r="F133">
         <v>1365</v>
@@ -9570,7 +9570,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.28839999999999999</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="F134">
         <v>1365</v>
@@ -9605,7 +9605,7 @@
         <v>14</v>
       </c>
       <c r="E135">
-        <v>0.28839999999999999</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="F135">
         <v>1365</v>
@@ -9640,7 +9640,7 @@
         <v>14</v>
       </c>
       <c r="E136">
-        <v>0.24784375000000003</v>
+        <v>0.21066718750000002</v>
       </c>
       <c r="F136">
         <v>1365</v>
@@ -9675,7 +9675,7 @@
         <v>14</v>
       </c>
       <c r="E137">
-        <v>0.27938750000000001</v>
+        <v>0.23747937499999999</v>
       </c>
       <c r="F137">
         <v>1365</v>
@@ -9710,7 +9710,7 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F138">
         <v>1365</v>
@@ -9745,7 +9745,7 @@
         <v>14</v>
       </c>
       <c r="E139">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F139">
         <v>1365</v>
@@ -9780,7 +9780,7 @@
         <v>14</v>
       </c>
       <c r="E140">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F140">
         <v>1365</v>
@@ -9815,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="E141">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F141">
         <v>1365</v>
@@ -9850,7 +9850,7 @@
         <v>14</v>
       </c>
       <c r="E142">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F142">
         <v>1365</v>
@@ -9885,7 +9885,7 @@
         <v>14</v>
       </c>
       <c r="E143">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F143">
         <v>1365</v>
@@ -9920,7 +9920,7 @@
         <v>14</v>
       </c>
       <c r="E144">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F144">
         <v>1365</v>
@@ -9955,7 +9955,7 @@
         <v>14</v>
       </c>
       <c r="E145">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F145">
         <v>1365</v>
@@ -9990,7 +9990,7 @@
         <v>14</v>
       </c>
       <c r="E146">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F146">
         <v>1365</v>
@@ -10025,7 +10025,7 @@
         <v>14</v>
       </c>
       <c r="E147">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F147">
         <v>1365</v>
@@ -10060,7 +10060,7 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F148">
         <v>1365</v>
@@ -10095,7 +10095,7 @@
         <v>14</v>
       </c>
       <c r="E149">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F149">
         <v>1365</v>
@@ -10130,7 +10130,7 @@
         <v>14</v>
       </c>
       <c r="E150">
-        <v>0.27592115384615384</v>
+        <v>0.23453298076923076</v>
       </c>
       <c r="F150">
         <v>1365</v>
@@ -10165,7 +10165,7 @@
         <v>14</v>
       </c>
       <c r="E151">
-        <v>0.32445000000000007</v>
+        <v>0.2757825000000001</v>
       </c>
       <c r="F151">
         <v>1365</v>
@@ -10200,7 +10200,7 @@
         <v>14</v>
       </c>
       <c r="E152">
-        <v>0.32445000000000007</v>
+        <v>0.2757825000000001</v>
       </c>
       <c r="F152">
         <v>1365</v>
@@ -10235,7 +10235,7 @@
         <v>14</v>
       </c>
       <c r="E153">
-        <v>0.32445000000000007</v>
+        <v>0.2757825000000001</v>
       </c>
       <c r="F153">
         <v>1365</v>
@@ -10270,7 +10270,7 @@
         <v>14</v>
       </c>
       <c r="E154">
-        <v>0.32445000000000007</v>
+        <v>0.2757825000000001</v>
       </c>
       <c r="F154">
         <v>1365</v>
@@ -10305,7 +10305,7 @@
         <v>14</v>
       </c>
       <c r="E155">
-        <v>0.32445000000000007</v>
+        <v>0.2757825000000001</v>
       </c>
       <c r="F155">
         <v>1365</v>
@@ -10340,7 +10340,7 @@
         <v>14</v>
       </c>
       <c r="E156">
-        <v>0.32445000000000007</v>
+        <v>0.2757825000000001</v>
       </c>
       <c r="F156">
         <v>1365</v>
@@ -10375,7 +10375,7 @@
         <v>14</v>
       </c>
       <c r="E157">
-        <v>0.27938750000000001</v>
+        <v>0.23747937499999999</v>
       </c>
       <c r="F157">
         <v>1365</v>
@@ -10410,7 +10410,7 @@
         <v>14</v>
       </c>
       <c r="E158">
-        <v>0.27938750000000001</v>
+        <v>0.23747937499999999</v>
       </c>
       <c r="F158">
         <v>1365</v>
@@ -10445,7 +10445,7 @@
         <v>14</v>
       </c>
       <c r="E159">
-        <v>0.27938750000000001</v>
+        <v>0.23747937499999999</v>
       </c>
       <c r="F159">
         <v>1365</v>
@@ -10480,7 +10480,7 @@
         <v>14</v>
       </c>
       <c r="E160">
-        <v>0.31093124999999999</v>
+        <v>0.26429156249999997</v>
       </c>
       <c r="F160">
         <v>1365</v>
@@ -10515,7 +10515,7 @@
         <v>14</v>
       </c>
       <c r="E161">
-        <v>0.30191875000000001</v>
+        <v>0.25663093749999999</v>
       </c>
       <c r="F161">
         <v>1365</v>
@@ -10550,7 +10550,7 @@
         <v>14</v>
       </c>
       <c r="E162">
-        <v>0.30191875000000001</v>
+        <v>0.25663093749999999</v>
       </c>
       <c r="F162">
         <v>1365</v>
@@ -10585,7 +10585,7 @@
         <v>14</v>
       </c>
       <c r="E163">
-        <v>0.30191875000000001</v>
+        <v>0.25663093749999999</v>
       </c>
       <c r="F163">
         <v>1365</v>
@@ -10620,7 +10620,7 @@
         <v>14</v>
       </c>
       <c r="E164">
-        <v>0.30191875000000001</v>
+        <v>0.25663093749999999</v>
       </c>
       <c r="F164">
         <v>1365</v>
@@ -10655,7 +10655,7 @@
         <v>14</v>
       </c>
       <c r="E165">
-        <v>0.30191875000000001</v>
+        <v>0.25663093749999999</v>
       </c>
       <c r="F165">
         <v>1365</v>
@@ -10690,7 +10690,7 @@
         <v>14</v>
       </c>
       <c r="E166">
-        <v>0.30191875000000001</v>
+        <v>0.25663093749999999</v>
       </c>
       <c r="F166">
         <v>1365</v>
@@ -10725,7 +10725,7 @@
         <v>14</v>
       </c>
       <c r="E167">
-        <v>0.30191875000000001</v>
+        <v>0.25663093749999999</v>
       </c>
       <c r="F167">
         <v>1365</v>
@@ -10760,7 +10760,7 @@
         <v>14</v>
       </c>
       <c r="E168">
-        <v>0.41457500000000003</v>
+        <v>0.35238875000000003</v>
       </c>
       <c r="F168">
         <v>1365</v>
@@ -10795,7 +10795,7 @@
         <v>14</v>
       </c>
       <c r="E169">
-        <v>0.41457500000000003</v>
+        <v>0.35238875000000003</v>
       </c>
       <c r="F169">
         <v>1365</v>
@@ -10830,7 +10830,7 @@
         <v>14</v>
       </c>
       <c r="E170">
-        <v>0.41457500000000003</v>
+        <v>0.35238875000000003</v>
       </c>
       <c r="F170">
         <v>1365</v>
@@ -10865,7 +10865,7 @@
         <v>14</v>
       </c>
       <c r="E171">
-        <v>0.24333750000000001</v>
+        <v>0.206836875</v>
       </c>
       <c r="F171">
         <v>1365</v>
@@ -10900,7 +10900,7 @@
         <v>14</v>
       </c>
       <c r="E172">
-        <v>0.22981874999999999</v>
+        <v>0.19534593749999996</v>
       </c>
       <c r="F172">
         <v>1365</v>
@@ -10935,7 +10935,7 @@
         <v>14</v>
       </c>
       <c r="E173">
-        <v>0.28839999999999999</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="F173">
         <v>1365</v>
@@ -10970,7 +10970,7 @@
         <v>14</v>
       </c>
       <c r="E174">
-        <v>0.28839999999999999</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="F174">
         <v>1365</v>
@@ -11005,7 +11005,7 @@
         <v>14</v>
       </c>
       <c r="E175">
-        <v>0.27037500000000003</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F175">
         <v>1365</v>
@@ -11040,7 +11040,7 @@
         <v>14</v>
       </c>
       <c r="E176">
-        <v>0.27037500000000003</v>
+        <v>0.22981874999999999</v>
       </c>
       <c r="F176">
         <v>1365</v>
@@ -11075,7 +11075,7 @@
         <v>14</v>
       </c>
       <c r="E177">
-        <v>0.29741250000000002</v>
+        <v>0.25280062500000006</v>
       </c>
       <c r="F177">
         <v>1365</v>
@@ -11110,7 +11110,7 @@
         <v>14</v>
       </c>
       <c r="E178">
-        <v>0.29741250000000002</v>
+        <v>0.25280062500000006</v>
       </c>
       <c r="F178">
         <v>1365</v>
@@ -11145,7 +11145,7 @@
         <v>14</v>
       </c>
       <c r="E179">
-        <v>0.29741250000000002</v>
+        <v>0.25280062500000006</v>
       </c>
       <c r="F179">
         <v>1365</v>
@@ -11180,7 +11180,7 @@
         <v>14</v>
       </c>
       <c r="E180">
-        <v>0.29741250000000002</v>
+        <v>0.25280062500000006</v>
       </c>
       <c r="F180">
         <v>1365</v>
@@ -11215,7 +11215,7 @@
         <v>14</v>
       </c>
       <c r="E181">
-        <v>0.29741250000000002</v>
+        <v>0.25280062500000006</v>
       </c>
       <c r="F181">
         <v>1365</v>
@@ -11250,7 +11250,7 @@
         <v>14</v>
       </c>
       <c r="E182">
-        <v>0.29741250000000002</v>
+        <v>0.25280062500000006</v>
       </c>
       <c r="F182">
         <v>1365</v>
@@ -11280,7 +11280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2FC0B9-BD12-4C5D-9ABD-F544C3419AA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78A0E82-CCD3-4B05-B7B7-F3F1C7D066BD}">
   <dimension ref="B9:T362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11365,7 +11365,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="G11">
-        <v>0.23690000000000003</v>
+        <v>0.20136499999999999</v>
       </c>
       <c r="H11">
         <v>5197.5</v>
@@ -11418,7 +11418,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
       <c r="G12">
-        <v>0.28840000000000005</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="H12">
         <v>5197.5</v>
@@ -11471,7 +11471,7 @@
         <v>0.14499999999999999</v>
       </c>
       <c r="G13">
-        <v>0.28840000000000005</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="H13">
         <v>5197.5</v>
@@ -11524,7 +11524,7 @@
         <v>0.03</v>
       </c>
       <c r="G14">
-        <v>0.309</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H14">
         <v>5197.5</v>
@@ -11577,7 +11577,7 @@
         <v>3.58</v>
       </c>
       <c r="G15">
-        <v>0.36049999999999999</v>
+        <v>0.306425</v>
       </c>
       <c r="H15">
         <v>3850.0000000000005</v>
@@ -11630,7 +11630,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
       <c r="G16">
-        <v>0.29869999999999997</v>
+        <v>0.25389499999999998</v>
       </c>
       <c r="H16">
         <v>4427.5</v>
@@ -11683,7 +11683,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G17">
-        <v>0.27295000000000003</v>
+        <v>0.23200749999999998</v>
       </c>
       <c r="H17">
         <v>4427.5</v>
@@ -11736,7 +11736,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G18">
-        <v>0.29869999999999997</v>
+        <v>0.25389499999999998</v>
       </c>
       <c r="H18">
         <v>4427.5</v>
@@ -11789,7 +11789,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="G19">
-        <v>0.29869999999999997</v>
+        <v>0.25389499999999998</v>
       </c>
       <c r="H19">
         <v>4427.5</v>
@@ -11842,7 +11842,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="G20">
-        <v>0.31930000000000003</v>
+        <v>0.27140500000000001</v>
       </c>
       <c r="H20">
         <v>4427.5</v>
@@ -11895,7 +11895,7 @@
         <v>1.6199999999999992</v>
       </c>
       <c r="G21">
-        <v>0.37080000000000002</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H21">
         <v>2200</v>
@@ -11948,7 +11948,7 @@
         <v>0.32</v>
       </c>
       <c r="G22">
-        <v>0.37080000000000002</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H22">
         <v>2200</v>
@@ -12001,7 +12001,7 @@
         <v>0.32</v>
       </c>
       <c r="G23">
-        <v>0.37080000000000002</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H23">
         <v>2200</v>
@@ -12054,7 +12054,7 @@
         <v>0.35</v>
       </c>
       <c r="G24">
-        <v>0.37080000000000002</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H24">
         <v>2200</v>
@@ -12107,7 +12107,7 @@
         <v>0.24</v>
       </c>
       <c r="G25">
-        <v>0.33990000000000004</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H25">
         <v>2530</v>
@@ -12160,7 +12160,7 @@
         <v>0.66</v>
       </c>
       <c r="G26">
-        <v>0.4017</v>
+        <v>0.341445</v>
       </c>
       <c r="H26">
         <v>2420</v>
@@ -12213,7 +12213,7 @@
         <v>0.66</v>
       </c>
       <c r="G27">
-        <v>0.4017</v>
+        <v>0.341445</v>
       </c>
       <c r="H27">
         <v>2420</v>
@@ -12266,7 +12266,7 @@
         <v>0.66</v>
       </c>
       <c r="G28">
-        <v>0.4017</v>
+        <v>0.341445</v>
       </c>
       <c r="H28">
         <v>2420</v>
@@ -12319,7 +12319,7 @@
         <v>0.66</v>
       </c>
       <c r="G29">
-        <v>0.43259999999999993</v>
+        <v>0.36770999999999998</v>
       </c>
       <c r="H29">
         <v>2640</v>
@@ -12372,7 +12372,7 @@
         <v>0.66</v>
       </c>
       <c r="G30">
-        <v>0.43259999999999993</v>
+        <v>0.36770999999999998</v>
       </c>
       <c r="H30">
         <v>2640</v>
@@ -12425,7 +12425,7 @@
         <v>0.66</v>
       </c>
       <c r="G31">
-        <v>0.43259999999999993</v>
+        <v>0.36770999999999998</v>
       </c>
       <c r="H31">
         <v>2640</v>
@@ -12478,7 +12478,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="G32">
-        <v>0.44289999999999996</v>
+        <v>0.37646499999999999</v>
       </c>
       <c r="H32">
         <v>1265</v>
@@ -12531,7 +12531,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
       <c r="G33">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999992</v>
       </c>
       <c r="H33">
         <v>1265</v>
@@ -12584,7 +12584,7 @@
         <v>0.23100000000000001</v>
       </c>
       <c r="G34">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H34">
         <v>1265</v>
@@ -12637,7 +12637,7 @@
         <v>0.125</v>
       </c>
       <c r="G35">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H35">
         <v>1265</v>
@@ -12690,7 +12690,7 @@
         <v>0.13700000000000001</v>
       </c>
       <c r="G36">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H36">
         <v>1265</v>
@@ -12743,7 +12743,7 @@
         <v>0.106</v>
       </c>
       <c r="G37">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H37">
         <v>1265</v>
@@ -12796,7 +12796,7 @@
         <v>0.05</v>
       </c>
       <c r="G38">
-        <v>0.49439999999999995</v>
+        <v>0.42024</v>
       </c>
       <c r="H38">
         <v>1485.0000000000002</v>
@@ -12849,7 +12849,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="G39">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H39">
         <v>1265</v>
@@ -12902,7 +12902,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="G40">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H40">
         <v>1265</v>
@@ -12955,7 +12955,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G41">
-        <v>0.53560000000000008</v>
+        <v>0.45526000000000005</v>
       </c>
       <c r="H41">
         <v>1265</v>
@@ -13008,7 +13008,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G42">
-        <v>0.53560000000000008</v>
+        <v>0.45526000000000005</v>
       </c>
       <c r="H42">
         <v>1265</v>
@@ -13061,7 +13061,7 @@
         <v>0.06</v>
       </c>
       <c r="G43">
-        <v>0.53560000000000008</v>
+        <v>0.45526000000000005</v>
       </c>
       <c r="H43">
         <v>1265</v>
@@ -13114,7 +13114,7 @@
         <v>0.36799999999999999</v>
       </c>
       <c r="G44">
-        <v>0.53560000000000019</v>
+        <v>0.45526000000000011</v>
       </c>
       <c r="H44">
         <v>1265</v>
@@ -13167,7 +13167,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="G45">
-        <v>0.53560000000000008</v>
+        <v>0.45526000000000005</v>
       </c>
       <c r="H45">
         <v>1265</v>
@@ -13220,7 +13220,7 @@
         <v>0.05</v>
       </c>
       <c r="G46">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H46">
         <v>1485.0000000000002</v>
@@ -13273,7 +13273,7 @@
         <v>0.122</v>
       </c>
       <c r="G47">
-        <v>0.53560000000000008</v>
+        <v>0.45526000000000005</v>
       </c>
       <c r="H47">
         <v>1265</v>
@@ -13326,7 +13326,7 @@
         <v>0.17699999999999999</v>
       </c>
       <c r="G48">
-        <v>0.53071186440677975</v>
+        <v>0.45110508474576283</v>
       </c>
       <c r="H48">
         <v>1317.2033898305085</v>
@@ -13379,7 +13379,7 @@
         <v>0.20599999999999999</v>
       </c>
       <c r="G49">
-        <v>0.53560000000000008</v>
+        <v>0.45526000000000005</v>
       </c>
       <c r="H49">
         <v>1265</v>
@@ -13432,7 +13432,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G50">
-        <v>0.55620000000000003</v>
+        <v>0.47277000000000002</v>
       </c>
       <c r="H50">
         <v>1485.0000000000002</v>
@@ -13485,7 +13485,7 @@
         <v>0.104</v>
       </c>
       <c r="G51">
-        <v>0.57680000000000009</v>
+        <v>0.49028000000000005</v>
       </c>
       <c r="H51">
         <v>1265</v>
@@ -13538,7 +13538,7 @@
         <v>0.1545</v>
       </c>
       <c r="G52">
-        <v>0.56446666666666678</v>
+        <v>0.47979666666666665</v>
       </c>
       <c r="H52">
         <v>1396.715210355987</v>
@@ -13591,7 +13591,7 @@
         <v>11.787799999999997</v>
       </c>
       <c r="G53">
-        <v>0.61799999999999999</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H53">
         <v>1100</v>
@@ -13644,7 +13644,7 @@
         <v>0.80800000000000005</v>
       </c>
       <c r="G54">
-        <v>0.56135000000000002</v>
+        <v>0.47714750000000006</v>
       </c>
       <c r="H54">
         <v>1100</v>
@@ -13697,7 +13697,7 @@
         <v>0.8</v>
       </c>
       <c r="G55">
-        <v>0.59739999999999993</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H55">
         <v>1100</v>
@@ -13750,7 +13750,7 @@
         <v>0.23899999999999999</v>
       </c>
       <c r="G56">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H56">
         <v>1265</v>
@@ -13803,7 +13803,7 @@
         <v>0.8</v>
       </c>
       <c r="G57">
-        <v>0.59739999999999993</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H57">
         <v>1100</v>
@@ -13856,7 +13856,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G58">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H58">
         <v>1100</v>
@@ -13909,7 +13909,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G59">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H59">
         <v>1100</v>
@@ -13962,7 +13962,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G60">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H60">
         <v>1100</v>
@@ -14015,7 +14015,7 @@
         <v>0.40100000000000002</v>
       </c>
       <c r="G61">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H61">
         <v>1100</v>
@@ -14068,7 +14068,7 @@
         <v>0.84799999999999998</v>
       </c>
       <c r="G62">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H62">
         <v>1100</v>
@@ -14121,7 +14121,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="G63">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999992</v>
       </c>
       <c r="H63">
         <v>1265</v>
@@ -14174,7 +14174,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="G64">
-        <v>0.54075000000000006</v>
+        <v>0.45963750000000003</v>
       </c>
       <c r="H64">
         <v>1100</v>
@@ -14227,7 +14227,7 @@
         <v>0.753</v>
       </c>
       <c r="G65">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H65">
         <v>1100</v>
@@ -14280,7 +14280,7 @@
         <v>0.37</v>
       </c>
       <c r="G66">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H66">
         <v>1100</v>
@@ -14333,7 +14333,7 @@
         <v>0.39</v>
       </c>
       <c r="G67">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H67">
         <v>1100</v>
@@ -14386,7 +14386,7 @@
         <v>0.39</v>
       </c>
       <c r="G68">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H68">
         <v>1100</v>
@@ -14439,7 +14439,7 @@
         <v>0.23</v>
       </c>
       <c r="G69">
-        <v>0.53560000000000008</v>
+        <v>0.45526000000000005</v>
       </c>
       <c r="H69">
         <v>1265</v>
@@ -14492,7 +14492,7 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="G70">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H70">
         <v>1100</v>
@@ -14545,7 +14545,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G71">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H71">
         <v>1100</v>
@@ -14598,7 +14598,7 @@
         <v>0.42</v>
       </c>
       <c r="G72">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H72">
         <v>1100</v>
@@ -14651,7 +14651,7 @@
         <v>0.42</v>
       </c>
       <c r="G73">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H73">
         <v>1100</v>
@@ -14704,7 +14704,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G74">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H74">
         <v>1100</v>
@@ -14757,7 +14757,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G75">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H75">
         <v>1100</v>
@@ -14810,7 +14810,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G76">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H76">
         <v>1100</v>
@@ -14863,7 +14863,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G77">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H77">
         <v>1100</v>
@@ -14916,7 +14916,7 @@
         <v>0.34499999999999997</v>
       </c>
       <c r="G78">
-        <v>0.54075000000000006</v>
+        <v>0.45963750000000003</v>
       </c>
       <c r="H78">
         <v>1100</v>
@@ -14969,7 +14969,7 @@
         <v>0.33700000000000002</v>
       </c>
       <c r="G79">
-        <v>0.54075000000000006</v>
+        <v>0.45963750000000003</v>
       </c>
       <c r="H79">
         <v>1100</v>
@@ -15022,7 +15022,7 @@
         <v>0.38</v>
       </c>
       <c r="G80">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H80">
         <v>1100</v>
@@ -15075,7 +15075,7 @@
         <v>0.78</v>
       </c>
       <c r="G81">
-        <v>0.61799999999999999</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H81">
         <v>1100</v>
@@ -15128,7 +15128,7 @@
         <v>0.76600000000000001</v>
       </c>
       <c r="G82">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H82">
         <v>1100</v>
@@ -15181,7 +15181,7 @@
         <v>0.155</v>
       </c>
       <c r="G83">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H83">
         <v>1265</v>
@@ -15234,7 +15234,7 @@
         <v>0.8</v>
       </c>
       <c r="G84">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H84">
         <v>1100</v>
@@ -15287,7 +15287,7 @@
         <v>0.4</v>
       </c>
       <c r="G85">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H85">
         <v>1100</v>
@@ -15340,7 +15340,7 @@
         <v>0.38</v>
       </c>
       <c r="G86">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H86">
         <v>1100</v>
@@ -15393,7 +15393,7 @@
         <v>0.30499999999999999</v>
       </c>
       <c r="G87">
-        <v>0.54075000000000006</v>
+        <v>0.45963749999999998</v>
       </c>
       <c r="H87">
         <v>1100</v>
@@ -15446,7 +15446,7 @@
         <v>0.30499999999999999</v>
       </c>
       <c r="G88">
-        <v>0.54075000000000006</v>
+        <v>0.45963749999999998</v>
       </c>
       <c r="H88">
         <v>1100</v>
@@ -15499,7 +15499,7 @@
         <v>0.24</v>
       </c>
       <c r="G89">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H89">
         <v>1265</v>
@@ -15552,7 +15552,7 @@
         <v>0.24</v>
       </c>
       <c r="G90">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H90">
         <v>1265</v>
@@ -15605,7 +15605,7 @@
         <v>0.4</v>
       </c>
       <c r="G91">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H91">
         <v>1100</v>
@@ -15658,7 +15658,7 @@
         <v>0.48</v>
       </c>
       <c r="G92">
-        <v>0.5613499999999999</v>
+        <v>0.4771475</v>
       </c>
       <c r="H92">
         <v>1100</v>
@@ -15711,7 +15711,7 @@
         <v>0.39200000000000002</v>
       </c>
       <c r="G93">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H93">
         <v>1100</v>
@@ -15764,7 +15764,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="G94">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H94">
         <v>1100</v>
@@ -15817,7 +15817,7 @@
         <v>0.80600000000000005</v>
       </c>
       <c r="G95">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H95">
         <v>1100</v>
@@ -15870,7 +15870,7 @@
         <v>0.36499999999999999</v>
       </c>
       <c r="G96">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H96">
         <v>1100</v>
@@ -15923,7 +15923,7 @@
         <v>0.4</v>
       </c>
       <c r="G97">
-        <v>0.46350000000000002</v>
+        <v>0.39397500000000002</v>
       </c>
       <c r="H97">
         <v>1100</v>
@@ -15976,7 +15976,7 @@
         <v>0.35</v>
       </c>
       <c r="G98">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H98">
         <v>1100</v>
@@ -16029,7 +16029,7 @@
         <v>0.36799999999999999</v>
       </c>
       <c r="G99">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H99">
         <v>1100</v>
@@ -16082,7 +16082,7 @@
         <v>0.36</v>
       </c>
       <c r="G100">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H100">
         <v>1100</v>
@@ -16135,7 +16135,7 @@
         <v>0.38300000000000001</v>
       </c>
       <c r="G101">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H101">
         <v>1100</v>
@@ -16188,7 +16188,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="G102">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H102">
         <v>1100</v>
@@ -16241,7 +16241,7 @@
         <v>0.38400000000000001</v>
       </c>
       <c r="G103">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H103">
         <v>1100</v>
@@ -16294,7 +16294,7 @@
         <v>0.18</v>
       </c>
       <c r="G104">
-        <v>0.57680000000000009</v>
+        <v>0.49028000000000005</v>
       </c>
       <c r="H104">
         <v>1265</v>
@@ -16347,7 +16347,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G105">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H105">
         <v>1100</v>
@@ -16400,7 +16400,7 @@
         <v>0.38100000000000001</v>
       </c>
       <c r="G106">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H106">
         <v>1100</v>
@@ -16453,7 +16453,7 @@
         <v>0.42099999999999999</v>
       </c>
       <c r="G107">
-        <v>0.59739999999999993</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H107">
         <v>1100</v>
@@ -16506,7 +16506,7 @@
         <v>0.39200000000000002</v>
       </c>
       <c r="G108">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H108">
         <v>1100</v>
@@ -16559,7 +16559,7 @@
         <v>0.40699999999999997</v>
       </c>
       <c r="G109">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H109">
         <v>1100</v>
@@ -16612,7 +16612,7 @@
         <v>0.40699999999999997</v>
       </c>
       <c r="G110">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H110">
         <v>1100</v>
@@ -16665,7 +16665,7 @@
         <v>0.38500000000000001</v>
       </c>
       <c r="G111">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H111">
         <v>1100</v>
@@ -16718,7 +16718,7 @@
         <v>0.76600000000000001</v>
       </c>
       <c r="G112">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H112">
         <v>1100</v>
@@ -16771,7 +16771,7 @@
         <v>0.88500000000000001</v>
       </c>
       <c r="G113">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H113">
         <v>1100</v>
@@ -16824,7 +16824,7 @@
         <v>0.38</v>
       </c>
       <c r="G114">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H114">
         <v>1100</v>
@@ -16877,7 +16877,7 @@
         <v>0.38</v>
       </c>
       <c r="G115">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H115">
         <v>1100</v>
@@ -16930,7 +16930,7 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="G116">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H116">
         <v>1100</v>
@@ -16983,7 +16983,7 @@
         <v>0.38500000000000001</v>
       </c>
       <c r="G117">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H117">
         <v>1100</v>
@@ -17036,7 +17036,7 @@
         <v>0.32</v>
       </c>
       <c r="G118">
-        <v>0.59739999999999993</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H118">
         <v>1100</v>
@@ -17089,7 +17089,7 @@
         <v>0.78</v>
       </c>
       <c r="G119">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H119">
         <v>1100</v>
@@ -17142,7 +17142,7 @@
         <v>0.76900000000000002</v>
       </c>
       <c r="G120">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H120">
         <v>1100</v>
@@ -17195,7 +17195,7 @@
         <v>0.39500000000000002</v>
       </c>
       <c r="G121">
-        <v>0.59739999999999993</v>
+        <v>0.50778999999999996</v>
       </c>
       <c r="H121">
         <v>1100</v>
@@ -17248,7 +17248,7 @@
         <v>0.76</v>
       </c>
       <c r="G122">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H122">
         <v>1100</v>
@@ -17301,7 +17301,7 @@
         <v>0.38</v>
       </c>
       <c r="G123">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H123">
         <v>1100</v>
@@ -17354,7 +17354,7 @@
         <v>0.86699999999999999</v>
       </c>
       <c r="G124">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H124">
         <v>1100</v>
@@ -17407,7 +17407,7 @@
         <v>0.85499999999999998</v>
       </c>
       <c r="G125">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H125">
         <v>1100</v>
@@ -17460,7 +17460,7 @@
         <v>0.8</v>
       </c>
       <c r="G126">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H126">
         <v>1100</v>
@@ -17513,7 +17513,7 @@
         <v>0.4</v>
       </c>
       <c r="G127">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H127">
         <v>1100</v>
@@ -17566,7 +17566,7 @@
         <v>0.76500000000000001</v>
       </c>
       <c r="G128">
-        <v>0.61799999999999999</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H128">
         <v>1100</v>
@@ -17619,7 +17619,7 @@
         <v>0.86</v>
       </c>
       <c r="G129">
-        <v>0.61799999999999999</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H129">
         <v>1100</v>
@@ -17672,7 +17672,7 @@
         <v>0.43</v>
       </c>
       <c r="G130">
-        <v>0.61799999999999999</v>
+        <v>0.52529999999999999</v>
       </c>
       <c r="H130">
         <v>1100</v>
@@ -17725,7 +17725,7 @@
         <v>0.39300000000000002</v>
       </c>
       <c r="G131">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H131">
         <v>1100</v>
@@ -17778,7 +17778,7 @@
         <v>0.38</v>
       </c>
       <c r="G132">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H132">
         <v>1100</v>
@@ -17831,7 +17831,7 @@
         <v>0.39200000000000002</v>
       </c>
       <c r="G133">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H133">
         <v>1100</v>
@@ -17884,7 +17884,7 @@
         <v>0.80500000000000005</v>
       </c>
       <c r="G134">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H134">
         <v>1100</v>
@@ -17937,7 +17937,7 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="G135">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H135">
         <v>1265</v>
@@ -17990,7 +17990,7 @@
         <v>0.25600000000000001</v>
       </c>
       <c r="G136">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H136">
         <v>1265</v>
@@ -18043,7 +18043,7 @@
         <v>0.56399999999999995</v>
       </c>
       <c r="G137">
-        <v>0.54075000000000006</v>
+        <v>0.45963750000000009</v>
       </c>
       <c r="H137">
         <v>1100</v>
@@ -18096,7 +18096,7 @@
         <v>0.23</v>
       </c>
       <c r="G138">
-        <v>0.51500000000000001</v>
+        <v>0.43774999999999997</v>
       </c>
       <c r="H138">
         <v>1265</v>
@@ -18149,7 +18149,7 @@
         <v>0.57499999999999996</v>
       </c>
       <c r="G139">
-        <v>0.56135000000000002</v>
+        <v>0.47714749999999995</v>
       </c>
       <c r="H139">
         <v>1100</v>
@@ -18202,7 +18202,7 @@
         <v>0.26</v>
       </c>
       <c r="G140">
-        <v>0.53560000000000008</v>
+        <v>0.45526000000000005</v>
       </c>
       <c r="H140">
         <v>1265</v>
@@ -18255,7 +18255,7 @@
         <v>0.18</v>
       </c>
       <c r="G141">
-        <v>0.53560000000000008</v>
+        <v>0.45526000000000005</v>
       </c>
       <c r="H141">
         <v>1265</v>
@@ -18308,7 +18308,7 @@
         <v>0.4</v>
       </c>
       <c r="G142">
-        <v>0.56135000000000002</v>
+        <v>0.4771475</v>
       </c>
       <c r="H142">
         <v>1100</v>
@@ -18361,7 +18361,7 @@
         <v>0.10779999999999999</v>
       </c>
       <c r="G143">
-        <v>0.25750000000000001</v>
+        <v>0.21887499999999999</v>
       </c>
       <c r="H143">
         <v>1012</v>
@@ -18414,7 +18414,7 @@
         <v>0.10779999999999999</v>
       </c>
       <c r="G144">
-        <v>0.25750000000000001</v>
+        <v>0.21887499999999999</v>
       </c>
       <c r="H144">
         <v>1012</v>
@@ -18467,7 +18467,7 @@
         <v>0.03</v>
       </c>
       <c r="G145">
-        <v>0.2472</v>
+        <v>0.21012</v>
       </c>
       <c r="H145">
         <v>1188</v>
@@ -18520,7 +18520,7 @@
         <v>0.248</v>
       </c>
       <c r="G146">
-        <v>0.27295000000000003</v>
+        <v>0.23200750000000001</v>
       </c>
       <c r="H146">
         <v>1012</v>
@@ -18573,7 +18573,7 @@
         <v>0.112</v>
       </c>
       <c r="G147">
-        <v>0.27295000000000003</v>
+        <v>0.23200750000000001</v>
       </c>
       <c r="H147">
         <v>1012</v>
@@ -18626,7 +18626,7 @@
         <v>0.112</v>
       </c>
       <c r="G148">
-        <v>0.27295000000000003</v>
+        <v>0.23200750000000001</v>
       </c>
       <c r="H148">
         <v>1012</v>
@@ -18679,7 +18679,7 @@
         <v>0.05</v>
       </c>
       <c r="G149">
-        <v>0.26264999999999999</v>
+        <v>0.22325249999999999</v>
       </c>
       <c r="H149">
         <v>1188</v>
@@ -18732,7 +18732,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G150">
-        <v>0.26264999999999999</v>
+        <v>0.22325249999999996</v>
       </c>
       <c r="H150">
         <v>1188</v>
@@ -18785,7 +18785,7 @@
         <v>0.05</v>
       </c>
       <c r="G151">
-        <v>0.28840000000000005</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="H151">
         <v>1188</v>
@@ -18838,7 +18838,7 @@
         <v>0.05</v>
       </c>
       <c r="G152">
-        <v>0.28840000000000005</v>
+        <v>0.24514000000000002</v>
       </c>
       <c r="H152">
         <v>1188</v>
@@ -18891,7 +18891,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G153">
-        <v>0.2884000000000001</v>
+        <v>0.24514</v>
       </c>
       <c r="H153">
         <v>1188</v>
@@ -18944,7 +18944,7 @@
         <v>0.13</v>
       </c>
       <c r="G154">
-        <v>0.31533846153846151</v>
+        <v>0.26803769230769231</v>
       </c>
       <c r="H154">
         <v>1079.6923076923076</v>
@@ -18997,7 +18997,7 @@
         <v>0.05</v>
       </c>
       <c r="G155">
-        <v>0.309</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H155">
         <v>1188</v>
@@ -19050,7 +19050,7 @@
         <v>0.8</v>
       </c>
       <c r="G156">
-        <v>0.33990000000000004</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H156">
         <v>880.00000000000011</v>
@@ -19103,7 +19103,7 @@
         <v>0.15</v>
       </c>
       <c r="G157">
-        <v>0.3296</v>
+        <v>0.28016000000000002</v>
       </c>
       <c r="H157">
         <v>1012</v>
@@ -19156,7 +19156,7 @@
         <v>0.15</v>
       </c>
       <c r="G158">
-        <v>0.3296</v>
+        <v>0.28016000000000002</v>
       </c>
       <c r="H158">
         <v>1012</v>
@@ -19209,7 +19209,7 @@
         <v>0.35599999999999998</v>
       </c>
       <c r="G159">
-        <v>0.28325000000000006</v>
+        <v>0.24076250000000005</v>
       </c>
       <c r="H159">
         <v>880.00000000000011</v>
@@ -19262,7 +19262,7 @@
         <v>0.23599999999999999</v>
       </c>
       <c r="G160">
-        <v>0.31930000000000003</v>
+        <v>0.27140500000000001</v>
       </c>
       <c r="H160">
         <v>1012</v>
@@ -19315,7 +19315,7 @@
         <v>3.15E-2</v>
       </c>
       <c r="G161">
-        <v>0.33990000000000004</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H161">
         <v>1633.5000000000002</v>
@@ -19368,7 +19368,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
       <c r="G162">
-        <v>0.33990000000000004</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H162">
         <v>1633.5000000000002</v>
@@ -19421,7 +19421,7 @@
         <v>2.46E-2</v>
       </c>
       <c r="G163">
-        <v>0.36564999999999998</v>
+        <v>0.31080249999999998</v>
       </c>
       <c r="H163">
         <v>1633.5000000000002</v>
@@ -19474,7 +19474,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="G164">
-        <v>0.37080000000000002</v>
+        <v>0.31518000000000007</v>
       </c>
       <c r="H164">
         <v>1391.5</v>
@@ -19527,7 +19527,7 @@
         <v>0.26080000000000003</v>
       </c>
       <c r="G165">
-        <v>0.37080000000000002</v>
+        <v>0.31517999999999996</v>
       </c>
       <c r="H165">
         <v>1430.4723926380368</v>
@@ -19580,7 +19580,7 @@
         <v>0.108</v>
       </c>
       <c r="G166">
-        <v>0.37080000000000007</v>
+        <v>0.31518000000000002</v>
       </c>
       <c r="H166">
         <v>1391.5</v>
@@ -19633,7 +19633,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G167">
-        <v>0.309</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H167">
         <v>1518.0000000000002</v>
@@ -19686,7 +19686,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
       <c r="G168">
-        <v>0.29869999999999997</v>
+        <v>0.25389499999999998</v>
       </c>
       <c r="H168">
         <v>1782.0000000000002</v>
@@ -19739,7 +19739,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G169">
-        <v>0.31930000000000003</v>
+        <v>0.27140500000000001</v>
       </c>
       <c r="H169">
         <v>1518.0000000000002</v>
@@ -19792,7 +19792,7 @@
         <v>3.1E-2</v>
       </c>
       <c r="G170">
-        <v>0.309</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H170">
         <v>1782.0000000000002</v>
@@ -19845,7 +19845,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G171">
-        <v>0.31930000000000003</v>
+        <v>0.27140500000000001</v>
       </c>
       <c r="H171">
         <v>1782.0000000000002</v>
@@ -19898,7 +19898,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G172">
-        <v>0.3296</v>
+        <v>0.28016000000000002</v>
       </c>
       <c r="H172">
         <v>1518.0000000000002</v>
@@ -19951,7 +19951,7 @@
         <v>0.02</v>
       </c>
       <c r="G173">
-        <v>0.34505000000000002</v>
+        <v>0.29329250000000001</v>
       </c>
       <c r="H173">
         <v>1782.0000000000005</v>
@@ -20004,7 +20004,7 @@
         <v>0.16</v>
       </c>
       <c r="G174">
-        <v>0.31930000000000003</v>
+        <v>0.27140500000000001</v>
       </c>
       <c r="H174">
         <v>1518.0000000000002</v>
@@ -20057,7 +20057,7 @@
         <v>0.16</v>
       </c>
       <c r="G175">
-        <v>0.31930000000000003</v>
+        <v>0.27140500000000001</v>
       </c>
       <c r="H175">
         <v>1518.0000000000002</v>
@@ -20110,7 +20110,7 @@
         <v>0.16</v>
       </c>
       <c r="G176">
-        <v>0.31930000000000003</v>
+        <v>0.27140500000000001</v>
       </c>
       <c r="H176">
         <v>1518.0000000000002</v>
@@ -20163,7 +20163,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="G177">
-        <v>0.35535</v>
+        <v>0.30204749999999997</v>
       </c>
       <c r="H177">
         <v>1518.0000000000002</v>
@@ -25451,7 +25451,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="G295">
-        <v>0.3296</v>
+        <v>0.28016000000000002</v>
       </c>
       <c r="H295">
         <v>1633.5000000000002</v>
@@ -25483,7 +25483,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="G296">
-        <v>0.35020000000000001</v>
+        <v>0.29766999999999999</v>
       </c>
       <c r="H296">
         <v>1391.5</v>
@@ -25515,7 +25515,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="G297">
-        <v>0.47380000000000005</v>
+        <v>0.40273000000000003</v>
       </c>
       <c r="H297">
         <v>1633.5000000000002</v>
@@ -25547,7 +25547,7 @@
         <v>0.18</v>
       </c>
       <c r="G298">
-        <v>0.26264999999999999</v>
+        <v>0.22325249999999996</v>
       </c>
       <c r="H298">
         <v>1138.5</v>
@@ -25579,7 +25579,7 @@
         <v>0.08</v>
       </c>
       <c r="G299">
-        <v>0.27810000000000001</v>
+        <v>0.23638500000000001</v>
       </c>
       <c r="H299">
         <v>1336.5</v>
@@ -25611,7 +25611,7 @@
         <v>0.21</v>
       </c>
       <c r="G300">
-        <v>0.29869999999999997</v>
+        <v>0.25389499999999998</v>
       </c>
       <c r="H300">
         <v>1644.4999999999998</v>
@@ -25643,7 +25643,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G301">
-        <v>0.29869999999999997</v>
+        <v>0.25389499999999998</v>
       </c>
       <c r="H301">
         <v>1644.4999999999998</v>
@@ -25675,7 +25675,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G302">
-        <v>0.309</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H302">
         <v>1644.4999999999998</v>
@@ -25707,7 +25707,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="G303">
-        <v>0.31930000000000003</v>
+        <v>0.27140500000000001</v>
       </c>
       <c r="H303">
         <v>1644.4999999999995</v>
@@ -25739,7 +25739,7 @@
         <v>0.1</v>
       </c>
       <c r="G304">
-        <v>0.33990000000000004</v>
+        <v>0.28891500000000003</v>
       </c>
       <c r="H304">
         <v>1644.4999999999998</v>
@@ -25771,7 +25771,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
       <c r="G305">
-        <v>0.33475000000000005</v>
+        <v>0.28453750000000005</v>
       </c>
       <c r="H305">
         <v>1930.5000000000002</v>
@@ -25803,7 +25803,7 @@
         <v>0.32</v>
       </c>
       <c r="G306">
-        <v>0.3296</v>
+        <v>0.28016000000000002</v>
       </c>
       <c r="H306">
         <v>1430.0000000000002</v>
@@ -25835,7 +25835,7 @@
         <v>0.32</v>
       </c>
       <c r="G307">
-        <v>0.3296</v>
+        <v>0.28016000000000002</v>
       </c>
       <c r="H307">
         <v>1430.0000000000002</v>
@@ -25867,7 +25867,7 @@
         <v>0.16</v>
       </c>
       <c r="G308">
-        <v>0.309</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H308">
         <v>1644.4999999999995</v>
@@ -25899,7 +25899,7 @@
         <v>0.16</v>
       </c>
       <c r="G309">
-        <v>0.309</v>
+        <v>0.26264999999999999</v>
       </c>
       <c r="H309">
         <v>1644.4999999999995</v>
@@ -26692,7 +26692,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L332">
-        <v>0.2182504394819377</v>
+        <v>0.21825043948193773</v>
       </c>
     </row>
     <row r="333" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F108C24C-7D65-4AC8-BFB2-E191EB1E4679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44D1E469-541F-40DD-A6BD-03992758B1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{9C22F052-05C5-4E21-8FE4-0D7575E8A6FD}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{47C57BA4-4BCD-4ACF-898D-466D1F568ECB}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2624,7 +2624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF4D1D26-975C-44D5-93F9-D46EB35553F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4979E4D5-E660-4A53-ABAB-F5ED569D4CCA}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11280,7 +11280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78A0E82-CCD3-4B05-B7B7-F3F1C7D066BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A34E0FA7-26F5-4140-ABB7-5F3A34749724}">
   <dimension ref="B9:T362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25946,7 +25946,7 @@
         <v>33</v>
       </c>
       <c r="L310">
-        <v>0.21912812891333872</v>
+        <v>0.21912812891333874</v>
       </c>
     </row>
     <row r="311" spans="2:12" x14ac:dyDescent="0.45">
@@ -26692,7 +26692,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L332">
-        <v>0.21825043948193773</v>
+        <v>0.21825043948193776</v>
       </c>
     </row>
     <row r="333" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44D1E469-541F-40DD-A6BD-03992758B1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBD40086-339F-4A17-AC1A-9ED00F5AB204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{47C57BA4-4BCD-4ACF-898D-466D1F568ECB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{35D425D2-5EE3-48B2-AE8C-703E74559EAA}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2624,7 +2624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4979E4D5-E660-4A53-ABAB-F5ED569D4CCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A938EC-6D4C-4AFA-8A8E-17D0BE6B19D6}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11280,7 +11280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A34E0FA7-26F5-4140-ABB7-5F3A34749724}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA12A3F-0B8F-4DDB-9E18-947BAD27CA8F}">
   <dimension ref="B9:T362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25946,7 +25946,7 @@
         <v>33</v>
       </c>
       <c r="L310">
-        <v>0.21912812891333874</v>
+        <v>0.21912812891333872</v>
       </c>
     </row>
     <row r="311" spans="2:12" x14ac:dyDescent="0.45">
@@ -26692,7 +26692,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L332">
-        <v>0.21825043948193776</v>
+        <v>0.2182504394819377</v>
       </c>
     </row>
     <row r="333" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBD40086-339F-4A17-AC1A-9ED00F5AB204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5520EF66-E149-47CF-AF4D-BE9C96266EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{35D425D2-5EE3-48B2-AE8C-703E74559EAA}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B1C8F160-758E-4E99-9C04-474614D5E596}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2624,7 +2624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A938EC-6D4C-4AFA-8A8E-17D0BE6B19D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E063679-4B7E-47FB-9673-6890ACDAFF1A}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11280,7 +11280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAA12A3F-0B8F-4DDB-9E18-947BAD27CA8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446BF0A3-AE9D-42FF-A82C-1D56BE79A46F}">
   <dimension ref="B9:T362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25946,7 +25946,7 @@
         <v>33</v>
       </c>
       <c r="L310">
-        <v>0.21912812891333872</v>
+        <v>0.21912812891333874</v>
       </c>
     </row>
     <row r="311" spans="2:12" x14ac:dyDescent="0.45">
@@ -26692,7 +26692,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L332">
-        <v>0.2182504394819377</v>
+        <v>0.21825043948193773</v>
       </c>
     </row>
     <row r="333" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5520EF66-E149-47CF-AF4D-BE9C96266EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{718D70D4-A93E-4C4A-9E71-7B5BACA643BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B1C8F160-758E-4E99-9C04-474614D5E596}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EAC3A2CB-721D-4B52-81EA-40A673713216}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2624,7 +2624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E063679-4B7E-47FB-9673-6890ACDAFF1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BE40F0-B663-4A26-8F5C-0F51402A07FB}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11280,7 +11280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{446BF0A3-AE9D-42FF-A82C-1D56BE79A46F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B494BDBE-FB53-4837-B00B-FA025EC8A11F}">
   <dimension ref="B9:T362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25946,7 +25946,7 @@
         <v>33</v>
       </c>
       <c r="L310">
-        <v>0.21912812891333874</v>
+        <v>0.21912812891333872</v>
       </c>
     </row>
     <row r="311" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{718D70D4-A93E-4C4A-9E71-7B5BACA643BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFA7F548-FB4D-4752-A92E-263B69D7ACE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{EAC3A2CB-721D-4B52-81EA-40A673713216}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8A20D001-82C4-4152-B8D8-56D9F56BF892}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2624,7 +2624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BE40F0-B663-4A26-8F5C-0F51402A07FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53DC792-1D3A-4123-A030-C8697B598E51}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11280,7 +11280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B494BDBE-FB53-4837-B00B-FA025EC8A11F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A8700E-C1BE-4620-BD69-CB3E0170B73E}">
   <dimension ref="B9:T362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25946,7 +25946,7 @@
         <v>33</v>
       </c>
       <c r="L310">
-        <v>0.21912812891333872</v>
+        <v>0.21912812891333874</v>
       </c>
     </row>
     <row r="311" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFA7F548-FB4D-4752-A92E-263B69D7ACE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60A78A48-C578-4950-969F-DC0FF58CB83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{8A20D001-82C4-4152-B8D8-56D9F56BF892}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C891F20E-58C9-4826-811D-AFA96A9C19F3}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2624,7 +2624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53DC792-1D3A-4123-A030-C8697B598E51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4424B3BC-9594-410E-A66E-C303EFA42EA0}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11280,7 +11280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A8700E-C1BE-4620-BD69-CB3E0170B73E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B97D122E-63AA-4CDE-81E0-87BE8AC5982B}">
   <dimension ref="B9:T362"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25946,7 +25946,7 @@
         <v>33</v>
       </c>
       <c r="L310">
-        <v>0.21912812891333874</v>
+        <v>0.21912812891333866</v>
       </c>
     </row>
     <row r="311" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D930929F-BA5A-40D0-9618-EC922BD11D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{155A32A9-E889-4A5C-BF4B-2095E596999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{036780DE-8017-46C2-A0E0-D8A8BDB76571}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{62BBDFE7-31B8-4025-BC46-64E814BC3A9F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2861,7 +2861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7636D6BD-702A-4780-8236-41EC57EE7808}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A87C9D-A7BD-45DC-82EE-4CFA92DEF904}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11517,7 +11517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7389B21-EB53-4A54-80F7-93312AA417B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690E2A7B-2BAB-4144-9F2D-FE34C42E265B}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29932,7 +29932,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L395">
-        <v>0.20575624785685132</v>
+        <v>0.20575624785685134</v>
       </c>
     </row>
     <row r="396" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{155A32A9-E889-4A5C-BF4B-2095E596999D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFC46127-C4E3-4574-ACBD-587BC560BD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{62BBDFE7-31B8-4025-BC46-64E814BC3A9F}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{DFFE0475-2522-4DDA-B1E1-6ED40D3D1EDD}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2861,7 +2861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A87C9D-A7BD-45DC-82EE-4CFA92DEF904}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8B1455-BBAE-44AA-B00E-D6C67EEEA957}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11517,7 +11517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690E2A7B-2BAB-4144-9F2D-FE34C42E265B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F024EB-9A05-49A3-8A89-09E87C6560B3}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFC46127-C4E3-4574-ACBD-587BC560BD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEF95BB4-7D66-48D0-82AF-5466251AEF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" xr2:uid="{DFFE0475-2522-4DDA-B1E1-6ED40D3D1EDD}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{015B9B41-C953-4123-A32F-350CD448C10F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2861,7 +2861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E8B1455-BBAE-44AA-B00E-D6C67EEEA957}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B26E105-1B7C-4CF2-BDCA-7539424A8B67}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11517,7 +11517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F024EB-9A05-49A3-8A89-09E87C6560B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25225EEB-066E-4763-9271-D5BB2F5B9B03}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -29932,7 +29932,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L395">
-        <v>0.20575624785685134</v>
+        <v>0.20575624785685132</v>
       </c>
     </row>
     <row r="396" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEF95BB4-7D66-48D0-82AF-5466251AEF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACF9D141-4FAC-4181-B61C-73CBA7C5B7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{015B9B41-C953-4123-A32F-350CD448C10F}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12683" xr2:uid="{29840571-C3B8-4A28-8F9F-4CB02FABA1C2}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2861,7 +2861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B26E105-1B7C-4CF2-BDCA-7539424A8B67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFCCD13-9757-4D59-8F3F-448861F54F96}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11517,7 +11517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25225EEB-066E-4763-9271-D5BB2F5B9B03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{164FA740-E856-4656-B622-BC6DC99BF1E9}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27100,7 +27100,7 @@
         <v>33</v>
       </c>
       <c r="L311">
-        <v>0.21137197268125332</v>
+        <v>0.2113719726812533</v>
       </c>
     </row>
     <row r="312" spans="2:12" x14ac:dyDescent="0.45">
@@ -29932,7 +29932,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L395">
-        <v>0.20575624785685132</v>
+        <v>0.20575624785685134</v>
       </c>
     </row>
     <row r="396" spans="2:12" x14ac:dyDescent="0.45">

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACF9D141-4FAC-4181-B61C-73CBA7C5B7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B3BE12D-B480-4368-9DD7-067F6C71569B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="21600" windowHeight="12683" xr2:uid="{29840571-C3B8-4A28-8F9F-4CB02FABA1C2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D4A2AF48-E82F-4F86-9746-1226CE2A65A5}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -945,13 +945,13 @@
     <t>elc_spv_024</t>
   </si>
   <si>
-    <t>ep_solar_thermal_012</t>
-  </si>
-  <si>
-    <t>ep_solar_thermal_013</t>
-  </si>
-  <si>
-    <t>ep_solar_thermal_014</t>
+    <t>ep_solar_thermal_019</t>
+  </si>
+  <si>
+    <t>ep_solar_thermal_020</t>
+  </si>
+  <si>
+    <t>ep_solar_thermal_022</t>
   </si>
   <si>
     <t>ep_windoff_wind</t>
@@ -2861,7 +2861,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFFCCD13-9757-4D59-8F3F-448861F54F96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{154AB1F1-A7D3-42AF-8EB8-EB6A7EBE2C92}">
   <dimension ref="B9:T182"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11517,7 +11517,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{164FA740-E856-4656-B622-BC6DC99BF1E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05267951-D83C-4FFC-9218-251202FC924D}">
   <dimension ref="B9:T516"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27100,7 +27100,7 @@
         <v>33</v>
       </c>
       <c r="L311">
-        <v>0.2113719726812533</v>
+        <v>0.21136545877859808</v>
       </c>
     </row>
     <row r="312" spans="2:12" x14ac:dyDescent="0.45">
@@ -27534,16 +27534,16 @@
         <v>273</v>
       </c>
       <c r="E324">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="F324">
-        <v>0.20680000000000001</v>
+        <v>2.1499999999999998E-2</v>
       </c>
       <c r="G324">
         <v>1</v>
       </c>
       <c r="H324">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I324">
         <v>21.450000000000003</v>
@@ -27552,10 +27552,10 @@
         <v>0</v>
       </c>
       <c r="K324">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L324">
-        <v>0.22101078675173377</v>
+        <v>0.17348833543116779</v>
       </c>
     </row>
     <row r="325" spans="2:12" x14ac:dyDescent="0.45">
@@ -27569,28 +27569,28 @@
         <v>273</v>
       </c>
       <c r="E325">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="F325">
-        <v>8.5000000000000006E-2</v>
+        <v>0.1004</v>
       </c>
       <c r="G325">
         <v>1</v>
       </c>
       <c r="H325">
-        <v>1210.7117647058824</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I325">
-        <v>19.353529411764708</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J325">
         <v>0</v>
       </c>
       <c r="K325">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L325">
-        <v>0.2198394615353855</v>
+        <v>0.17324856438753491</v>
       </c>
     </row>
     <row r="326" spans="2:12" x14ac:dyDescent="0.45">
@@ -27604,10 +27604,10 @@
         <v>275</v>
       </c>
       <c r="E326">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="F326">
-        <v>9.300000000000001E-3</v>
+        <v>1.8200000000000001E-2</v>
       </c>
       <c r="G326">
         <v>1</v>
@@ -27616,33 +27616,33 @@
         <v>1336.5</v>
       </c>
       <c r="I326">
-        <v>21.450000000000003</v>
+        <v>21.450000000000006</v>
       </c>
       <c r="J326">
         <v>0</v>
       </c>
       <c r="K326">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L326">
-        <v>0.22779083409784781</v>
+        <v>0.17579142700954378</v>
       </c>
     </row>
     <row r="327" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B327" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C327" t="s">
         <v>252</v>
       </c>
       <c r="D327" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E327">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="F327">
-        <v>5.7999999999999996E-3</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="G327">
         <v>1</v>
@@ -27657,27 +27657,27 @@
         <v>0</v>
       </c>
       <c r="K327">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L327">
-        <v>0.22779083409784781</v>
+        <v>0.2145221180349477</v>
       </c>
     </row>
     <row r="328" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B328" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C328" t="s">
         <v>252</v>
       </c>
       <c r="D328" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E328">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="F328">
-        <v>0.02</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="G328">
         <v>1</v>
@@ -27692,27 +27692,27 @@
         <v>0</v>
       </c>
       <c r="K328">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L328">
-        <v>0.22779083409784778</v>
+        <v>0.2145221180349477</v>
       </c>
     </row>
     <row r="329" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B329" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C329" t="s">
         <v>252</v>
       </c>
       <c r="D329" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E329">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="F329">
-        <v>7.3399999999999979E-2</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="G329">
         <v>1</v>
@@ -27721,86 +27721,86 @@
         <v>1336.5</v>
       </c>
       <c r="I329">
-        <v>21.450000000000017</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J329">
         <v>0</v>
       </c>
       <c r="K329">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L329">
-        <v>0.22254285010939953</v>
+        <v>0.21419359348149575</v>
       </c>
     </row>
     <row r="330" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B330" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C330" t="s">
         <v>252</v>
       </c>
       <c r="D330" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E330">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="F330">
-        <v>2.5999999999999999E-2</v>
+        <v>0.31230000000000013</v>
       </c>
       <c r="G330">
         <v>1</v>
       </c>
       <c r="H330">
-        <v>1336.5</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I330">
-        <v>21.450000000000003</v>
+        <v>21.449999999999996</v>
       </c>
       <c r="J330">
         <v>0</v>
       </c>
       <c r="K330">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L330">
-        <v>0.22779083409784781</v>
+        <v>0.21057056744960562</v>
       </c>
     </row>
     <row r="331" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B331" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C331" t="s">
         <v>252</v>
       </c>
       <c r="D331" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E331">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F331">
-        <v>5.0999999999999995E-3</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="G331">
         <v>1</v>
       </c>
       <c r="H331">
-        <v>1336.5</v>
+        <v>1258.7666666666667</v>
       </c>
       <c r="I331">
-        <v>21.450000000000003</v>
+        <v>20.154444444444447</v>
       </c>
       <c r="J331">
         <v>0</v>
       </c>
       <c r="K331">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L331">
-        <v>0.22330548534716901</v>
+        <v>0.2145221180349477</v>
       </c>
     </row>
     <row r="332" spans="2:12" x14ac:dyDescent="0.45">
@@ -27814,28 +27814,28 @@
         <v>277</v>
       </c>
       <c r="E332">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="F332">
-        <v>1.9299999999999998E-2</v>
+        <v>0.223</v>
       </c>
       <c r="G332">
         <v>1</v>
       </c>
       <c r="H332">
-        <v>1336.5</v>
+        <v>1138.5</v>
       </c>
       <c r="I332">
-        <v>21.450000000000003</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="J332">
         <v>0</v>
       </c>
       <c r="K332">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L332">
-        <v>0.22897581092516034</v>
+        <v>0.21267365757673162</v>
       </c>
     </row>
     <row r="333" spans="2:12" x14ac:dyDescent="0.45">
@@ -27849,63 +27849,63 @@
         <v>277</v>
       </c>
       <c r="E333">
-        <v>2015</v>
+        <v>2028</v>
       </c>
       <c r="F333">
-        <v>0.15100000000000002</v>
+        <v>0.15</v>
       </c>
       <c r="G333">
         <v>1</v>
       </c>
       <c r="H333">
-        <v>1249.9569536423842</v>
+        <v>1138.5</v>
       </c>
       <c r="I333">
-        <v>20.007615894039731</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="J333">
         <v>0</v>
       </c>
       <c r="K333">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L333">
-        <v>0.22929965432338417</v>
+        <v>0.21452211803494767</v>
       </c>
     </row>
     <row r="334" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B334" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C334" t="s">
         <v>252</v>
       </c>
       <c r="D334" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E334">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="F334">
-        <v>5.0999999999999997E-2</v>
+        <v>5.6799999999999996E-2</v>
       </c>
       <c r="G334">
         <v>1</v>
       </c>
       <c r="H334">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I334">
-        <v>18.150000000000002</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J334">
         <v>0</v>
       </c>
       <c r="K334">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="L334">
-        <v>0.22897581092516031</v>
+        <v>0.20981915329914508</v>
       </c>
     </row>
     <row r="335" spans="2:12" x14ac:dyDescent="0.45">
@@ -27919,10 +27919,10 @@
         <v>279</v>
       </c>
       <c r="E335">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="F335">
-        <v>7.6E-3</v>
+        <v>3.9899999999999998E-2</v>
       </c>
       <c r="G335">
         <v>1</v>
@@ -27937,10 +27937,10 @@
         <v>0</v>
       </c>
       <c r="K335">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L335">
-        <v>0.22621581035120261</v>
+        <v>0.20905853994181761</v>
       </c>
     </row>
     <row r="336" spans="2:12" x14ac:dyDescent="0.45">
@@ -27954,28 +27954,28 @@
         <v>279</v>
       </c>
       <c r="E336">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="F336">
-        <v>3.5700000000000003E-2</v>
+        <v>0.46879999999999988</v>
       </c>
       <c r="G336">
         <v>1</v>
       </c>
       <c r="H336">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I336">
-        <v>21.450000000000003</v>
+        <v>21.450000000000006</v>
       </c>
       <c r="J336">
         <v>0</v>
       </c>
       <c r="K336">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L336">
-        <v>0.23261826092713075</v>
+        <v>0.20645573625516284</v>
       </c>
     </row>
     <row r="337" spans="2:12" x14ac:dyDescent="0.45">
@@ -27989,28 +27989,28 @@
         <v>279</v>
       </c>
       <c r="E337">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="F337">
-        <v>9.4999999999999998E-3</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G337">
         <v>1</v>
       </c>
       <c r="H337">
-        <v>1336.5</v>
+        <v>1138.5</v>
       </c>
       <c r="I337">
-        <v>21.450000000000003</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="J337">
         <v>0</v>
       </c>
       <c r="K337">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L337">
-        <v>0.23546267084801317</v>
+        <v>0.2138278512842284</v>
       </c>
     </row>
     <row r="338" spans="2:12" x14ac:dyDescent="0.45">
@@ -28024,28 +28024,28 @@
         <v>279</v>
       </c>
       <c r="E338">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="F338">
-        <v>5.0000000000000001E-3</v>
+        <v>0.105</v>
       </c>
       <c r="G338">
         <v>1</v>
       </c>
       <c r="H338">
-        <v>1336.5</v>
+        <v>1223.3571428571429</v>
       </c>
       <c r="I338">
-        <v>21.450000000000003</v>
+        <v>19.56428571428572</v>
       </c>
       <c r="J338">
         <v>0</v>
       </c>
       <c r="K338">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="L338">
-        <v>0.22990287162581269</v>
+        <v>0.2115734559696158</v>
       </c>
     </row>
     <row r="339" spans="2:12" x14ac:dyDescent="0.45">
@@ -28059,10 +28059,10 @@
         <v>279</v>
       </c>
       <c r="E339">
-        <v>2015</v>
+        <v>2028</v>
       </c>
       <c r="F339">
-        <v>0.28910000000000002</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="G339">
         <v>1</v>
@@ -28071,68 +28071,68 @@
         <v>1336.5</v>
       </c>
       <c r="I339">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J339">
         <v>0</v>
       </c>
       <c r="K339">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L339">
-        <v>0.23157936681277738</v>
+        <v>0.20576891319722002</v>
       </c>
     </row>
     <row r="340" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B340" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C340" t="s">
         <v>252</v>
       </c>
       <c r="D340" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E340">
-        <v>2016</v>
+        <v>2010</v>
       </c>
       <c r="F340">
-        <v>0.01</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="G340">
         <v>1</v>
       </c>
       <c r="H340">
-        <v>1336.5</v>
+        <v>1154.1315789473683</v>
       </c>
       <c r="I340">
-        <v>21.450000000000003</v>
+        <v>18.410526315789479</v>
       </c>
       <c r="J340">
         <v>0</v>
       </c>
       <c r="K340">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L340">
-        <v>0.22990287162581269</v>
+        <v>0.18367495595626879</v>
       </c>
     </row>
     <row r="341" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B341" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C341" t="s">
         <v>252</v>
       </c>
       <c r="D341" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E341">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="F341">
-        <v>9.6999999999999986E-3</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="G341">
         <v>1</v>
@@ -28147,62 +28147,62 @@
         <v>0</v>
       </c>
       <c r="K341">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="L341">
-        <v>0.23546267084801323</v>
+        <v>0.1830157785160744</v>
       </c>
     </row>
     <row r="342" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B342" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C342" t="s">
         <v>252</v>
       </c>
       <c r="D342" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E342">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="F342">
-        <v>4.1000000000000002E-2</v>
+        <v>0.32480000000000003</v>
       </c>
       <c r="G342">
         <v>1</v>
       </c>
       <c r="H342">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I342">
-        <v>21.450000000000003</v>
+        <v>21.449999999999989</v>
       </c>
       <c r="J342">
         <v>0</v>
       </c>
       <c r="K342">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L342">
-        <v>0.22990287162581269</v>
+        <v>0.18637364754073979</v>
       </c>
     </row>
     <row r="343" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B343" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C343" t="s">
         <v>252</v>
       </c>
       <c r="D343" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E343">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F343">
-        <v>1.7999999999999999E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="G343">
         <v>1</v>
@@ -28217,33 +28217,33 @@
         <v>0</v>
       </c>
       <c r="K343">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L343">
-        <v>0.22990287162581266</v>
+        <v>0.1830157785160744</v>
       </c>
     </row>
     <row r="344" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B344" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C344" t="s">
         <v>252</v>
       </c>
       <c r="D344" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E344">
-        <v>2026</v>
+        <v>2015</v>
       </c>
       <c r="F344">
-        <v>3.7999999999999999E-2</v>
+        <v>0.20560000000000006</v>
       </c>
       <c r="G344">
         <v>1</v>
       </c>
       <c r="H344">
-        <v>1336.5</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I344">
         <v>21.450000000000003</v>
@@ -28252,68 +28252,68 @@
         <v>0</v>
       </c>
       <c r="K344">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L344">
-        <v>0.22817316965907841</v>
+        <v>0.19688949549367962</v>
       </c>
     </row>
     <row r="345" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B345" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C345" t="s">
         <v>252</v>
       </c>
       <c r="D345" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E345">
-        <v>2028</v>
+        <v>2011</v>
       </c>
       <c r="F345">
-        <v>9.3099999999999988E-2</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="G345">
         <v>1</v>
       </c>
       <c r="H345">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I345">
-        <v>18.150000000000002</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J345">
         <v>0</v>
       </c>
       <c r="K345">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L345">
-        <v>0.22735641515094751</v>
+        <v>0.19372001814840661</v>
       </c>
     </row>
     <row r="346" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B346" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C346" t="s">
         <v>252</v>
       </c>
       <c r="D346" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E346">
         <v>2015</v>
       </c>
       <c r="F346">
-        <v>0.13950000000000004</v>
+        <v>3.2699999999999993E-2</v>
       </c>
       <c r="G346">
         <v>1</v>
       </c>
       <c r="H346">
-        <v>1336.4999999999998</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I346">
         <v>21.450000000000006</v>
@@ -28325,30 +28325,30 @@
         <v>40</v>
       </c>
       <c r="L346">
-        <v>0.22263780528731941</v>
+        <v>0.18489803177812383</v>
       </c>
     </row>
     <row r="347" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B347" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C347" t="s">
         <v>252</v>
       </c>
       <c r="D347" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E347">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="F347">
-        <v>5.0000000000000001E-3</v>
+        <v>0.20680000000000001</v>
       </c>
       <c r="G347">
         <v>1</v>
       </c>
       <c r="H347">
-        <v>1336.5</v>
+        <v>1336.5000000000002</v>
       </c>
       <c r="I347">
         <v>21.450000000000003</v>
@@ -28357,62 +28357,62 @@
         <v>0</v>
       </c>
       <c r="K347">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L347">
-        <v>0.2200335851180813</v>
+        <v>0.22101078675173377</v>
       </c>
     </row>
     <row r="348" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B348" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C348" t="s">
         <v>252</v>
       </c>
       <c r="D348" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E348">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="F348">
-        <v>5.7700000000000001E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="G348">
         <v>1</v>
       </c>
       <c r="H348">
-        <v>1336.5</v>
+        <v>1210.7117647058824</v>
       </c>
       <c r="I348">
-        <v>21.450000000000003</v>
+        <v>19.353529411764708</v>
       </c>
       <c r="J348">
         <v>0</v>
       </c>
       <c r="K348">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="L348">
-        <v>0.22037760483842214</v>
+        <v>0.2198394615353855</v>
       </c>
     </row>
     <row r="349" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B349" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C349" t="s">
         <v>252</v>
       </c>
       <c r="D349" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E349">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="F349">
-        <v>2.0799999999999999E-2</v>
+        <v>9.300000000000001E-3</v>
       </c>
       <c r="G349">
         <v>1</v>
@@ -28427,27 +28427,27 @@
         <v>0</v>
       </c>
       <c r="K349">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L349">
-        <v>0.22057989228923436</v>
+        <v>0.22779083409784781</v>
       </c>
     </row>
     <row r="350" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B350" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C350" t="s">
         <v>252</v>
       </c>
       <c r="D350" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E350">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="F350">
-        <v>9.1999999999999998E-3</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G350">
         <v>1</v>
@@ -28462,62 +28462,62 @@
         <v>0</v>
       </c>
       <c r="K350">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L350">
-        <v>0.21997659078087359</v>
+        <v>0.22779083409784781</v>
       </c>
     </row>
     <row r="351" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B351" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C351" t="s">
         <v>252</v>
       </c>
       <c r="D351" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E351">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="F351">
-        <v>0.25670000000000009</v>
+        <v>0.02</v>
       </c>
       <c r="G351">
         <v>1</v>
       </c>
       <c r="H351">
-        <v>1336.4999999999993</v>
+        <v>1336.5</v>
       </c>
       <c r="I351">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J351">
         <v>0</v>
       </c>
       <c r="K351">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L351">
-        <v>0.22051250081948157</v>
+        <v>0.22779083409784778</v>
       </c>
     </row>
     <row r="352" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B352" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C352" t="s">
         <v>252</v>
       </c>
       <c r="D352" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E352">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="F352">
-        <v>3.78E-2</v>
+        <v>7.3399999999999979E-2</v>
       </c>
       <c r="G352">
         <v>1</v>
@@ -28526,33 +28526,33 @@
         <v>1336.5</v>
       </c>
       <c r="I352">
-        <v>21.450000000000006</v>
+        <v>21.450000000000017</v>
       </c>
       <c r="J352">
         <v>0</v>
       </c>
       <c r="K352">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L352">
-        <v>0.21133391274598409</v>
+        <v>0.22254285010939953</v>
       </c>
     </row>
     <row r="353" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B353" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C353" t="s">
         <v>252</v>
       </c>
       <c r="D353" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E353">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="F353">
-        <v>0.03</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="G353">
         <v>1</v>
@@ -28567,167 +28567,167 @@
         <v>0</v>
       </c>
       <c r="K353">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="L353">
-        <v>0.21706938938321105</v>
+        <v>0.22779083409784781</v>
       </c>
     </row>
     <row r="354" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B354" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C354" t="s">
         <v>252</v>
       </c>
       <c r="D354" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E354">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F354">
-        <v>0.18669999999999995</v>
+        <v>5.0999999999999995E-3</v>
       </c>
       <c r="G354">
         <v>1</v>
       </c>
       <c r="H354">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I354">
-        <v>21.45000000000001</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J354">
         <v>0</v>
       </c>
       <c r="K354">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L354">
-        <v>0.21407140711623759</v>
+        <v>0.22330548534716901</v>
       </c>
     </row>
     <row r="355" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B355" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C355" t="s">
         <v>252</v>
       </c>
       <c r="D355" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E355">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="F355">
-        <v>0.189</v>
+        <v>1.9299999999999998E-2</v>
       </c>
       <c r="G355">
         <v>1</v>
       </c>
       <c r="H355">
-        <v>1180.4047619047619</v>
+        <v>1336.5</v>
       </c>
       <c r="I355">
-        <v>18.848412698412702</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J355">
         <v>0</v>
       </c>
       <c r="K355">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L355">
-        <v>0.21045830299807192</v>
+        <v>0.22897581092516034</v>
       </c>
     </row>
     <row r="356" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B356" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C356" t="s">
         <v>252</v>
       </c>
       <c r="D356" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E356">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="F356">
-        <v>1.9E-2</v>
+        <v>0.15100000000000002</v>
       </c>
       <c r="G356">
         <v>1</v>
       </c>
       <c r="H356">
-        <v>1336.5</v>
+        <v>1249.9569536423842</v>
       </c>
       <c r="I356">
-        <v>21.450000000000003</v>
+        <v>20.007615894039731</v>
       </c>
       <c r="J356">
         <v>0</v>
       </c>
       <c r="K356">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L356">
-        <v>0.21831799184116799</v>
+        <v>0.22929965432338417</v>
       </c>
     </row>
     <row r="357" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B357" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C357" t="s">
         <v>252</v>
       </c>
       <c r="D357" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E357">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="F357">
-        <v>3.5000000000000003E-2</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="G357">
         <v>1</v>
       </c>
       <c r="H357">
-        <v>1336.5</v>
+        <v>1138.5</v>
       </c>
       <c r="I357">
-        <v>21.450000000000003</v>
+        <v>18.150000000000002</v>
       </c>
       <c r="J357">
         <v>0</v>
       </c>
       <c r="K357">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L357">
-        <v>0.21892389070522661</v>
+        <v>0.22897581092516031</v>
       </c>
     </row>
     <row r="358" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B358" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C358" t="s">
         <v>252</v>
       </c>
       <c r="D358" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E358">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="F358">
-        <v>2.1499999999999998E-2</v>
+        <v>7.6E-3</v>
       </c>
       <c r="G358">
         <v>1</v>
@@ -28742,33 +28742,33 @@
         <v>0</v>
       </c>
       <c r="K358">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L358">
-        <v>0.17348833543116779</v>
+        <v>0.22621581035120261</v>
       </c>
     </row>
     <row r="359" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B359" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C359" t="s">
         <v>252</v>
       </c>
       <c r="D359" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E359">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="F359">
-        <v>0.1004</v>
+        <v>3.5700000000000003E-2</v>
       </c>
       <c r="G359">
         <v>1</v>
       </c>
       <c r="H359">
-        <v>1336.4999999999998</v>
+        <v>1336.5</v>
       </c>
       <c r="I359">
         <v>21.450000000000003</v>
@@ -28777,27 +28777,27 @@
         <v>0</v>
       </c>
       <c r="K359">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L359">
-        <v>0.17324856438753491</v>
+        <v>0.23261826092713075</v>
       </c>
     </row>
     <row r="360" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B360" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C360" t="s">
         <v>252</v>
       </c>
       <c r="D360" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E360">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="F360">
-        <v>1.8200000000000001E-2</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="G360">
         <v>1</v>
@@ -28806,51 +28806,51 @@
         <v>1336.5</v>
       </c>
       <c r="I360">
-        <v>21.450000000000006</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J360">
         <v>0</v>
       </c>
       <c r="K360">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L360">
-        <v>0.17579142700954378</v>
+        <v>0.23546267084801317</v>
       </c>
     </row>
     <row r="361" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B361" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C361" t="s">
         <v>252</v>
       </c>
       <c r="D361" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E361">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F361">
-        <v>0.15690000000000001</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G361">
         <v>1</v>
       </c>
       <c r="H361">
-        <v>1336.4999999999998</v>
+        <v>1336.5</v>
       </c>
       <c r="I361">
-        <v>21.45</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J361">
         <v>0</v>
       </c>
       <c r="K361">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L361">
-        <v>0.20418013528360995</v>
+        <v>0.22990287162581269</v>
       </c>
     </row>
     <row r="362" spans="2:12" x14ac:dyDescent="0.45">
@@ -28864,10 +28864,10 @@
         <v>293</v>
       </c>
       <c r="E362">
-        <v>2009</v>
+        <v>2015</v>
       </c>
       <c r="F362">
-        <v>4.4999999999999998E-2</v>
+        <v>0.28910000000000002</v>
       </c>
       <c r="G362">
         <v>1</v>
@@ -28876,16 +28876,16 @@
         <v>1336.5</v>
       </c>
       <c r="I362">
-        <v>21.450000000000003</v>
+        <v>21.45</v>
       </c>
       <c r="J362">
         <v>0</v>
       </c>
       <c r="K362">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L362">
-        <v>0.2145221180349477</v>
+        <v>0.23157936681277738</v>
       </c>
     </row>
     <row r="363" spans="2:12" x14ac:dyDescent="0.45">
@@ -28899,10 +28899,10 @@
         <v>293</v>
       </c>
       <c r="E363">
-        <v>2010</v>
+        <v>2016</v>
       </c>
       <c r="F363">
-        <v>6.0000000000000001E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G363">
         <v>1</v>
@@ -28917,10 +28917,10 @@
         <v>0</v>
       </c>
       <c r="K363">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L363">
-        <v>0.2145221180349477</v>
+        <v>0.22990287162581269</v>
       </c>
     </row>
     <row r="364" spans="2:12" x14ac:dyDescent="0.45">
@@ -28934,10 +28934,10 @@
         <v>293</v>
       </c>
       <c r="E364">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="F364">
-        <v>0.10100000000000001</v>
+        <v>9.6999999999999986E-3</v>
       </c>
       <c r="G364">
         <v>1</v>
@@ -28952,10 +28952,10 @@
         <v>0</v>
       </c>
       <c r="K364">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="L364">
-        <v>0.21419359348149575</v>
+        <v>0.23546267084801323</v>
       </c>
     </row>
     <row r="365" spans="2:12" x14ac:dyDescent="0.45">
@@ -28969,28 +28969,28 @@
         <v>293</v>
       </c>
       <c r="E365">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="F365">
-        <v>0.31230000000000013</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="G365">
         <v>1</v>
       </c>
       <c r="H365">
-        <v>1336.4999999999998</v>
+        <v>1336.5</v>
       </c>
       <c r="I365">
-        <v>21.449999999999996</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J365">
         <v>0</v>
       </c>
       <c r="K365">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="L365">
-        <v>0.21057056744960562</v>
+        <v>0.22990287162581269</v>
       </c>
     </row>
     <row r="366" spans="2:12" x14ac:dyDescent="0.45">
@@ -29004,28 +29004,28 @@
         <v>293</v>
       </c>
       <c r="E366">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F366">
-        <v>0.13500000000000001</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="G366">
         <v>1</v>
       </c>
       <c r="H366">
-        <v>1258.7666666666667</v>
+        <v>1336.5</v>
       </c>
       <c r="I366">
-        <v>20.154444444444447</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J366">
         <v>0</v>
       </c>
       <c r="K366">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L366">
-        <v>0.2145221180349477</v>
+        <v>0.22990287162581266</v>
       </c>
     </row>
     <row r="367" spans="2:12" x14ac:dyDescent="0.45">
@@ -29039,19 +29039,19 @@
         <v>293</v>
       </c>
       <c r="E367">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F367">
-        <v>0.223</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="G367">
         <v>1</v>
       </c>
       <c r="H367">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I367">
-        <v>18.150000000000002</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J367">
         <v>0</v>
@@ -29060,7 +29060,7 @@
         <v>30</v>
       </c>
       <c r="L367">
-        <v>0.21267365757673162</v>
+        <v>0.22817316965907841</v>
       </c>
     </row>
     <row r="368" spans="2:12" x14ac:dyDescent="0.45">
@@ -29077,7 +29077,7 @@
         <v>2028</v>
       </c>
       <c r="F368">
-        <v>0.15</v>
+        <v>9.3099999999999988E-2</v>
       </c>
       <c r="G368">
         <v>1</v>
@@ -29095,7 +29095,7 @@
         <v>30</v>
       </c>
       <c r="L368">
-        <v>0.21452211803494767</v>
+        <v>0.22735641515094751</v>
       </c>
     </row>
     <row r="369" spans="2:12" x14ac:dyDescent="0.45">
@@ -29109,10 +29109,10 @@
         <v>295</v>
       </c>
       <c r="E369">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="F369">
-        <v>5.6799999999999996E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G369">
         <v>1</v>
@@ -29127,10 +29127,10 @@
         <v>0</v>
       </c>
       <c r="K369">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L369">
-        <v>0.20981915329914508</v>
+        <v>0.2200335851180813</v>
       </c>
     </row>
     <row r="370" spans="2:12" x14ac:dyDescent="0.45">
@@ -29144,10 +29144,10 @@
         <v>295</v>
       </c>
       <c r="E370">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="F370">
-        <v>3.9899999999999998E-2</v>
+        <v>5.7700000000000001E-2</v>
       </c>
       <c r="G370">
         <v>1</v>
@@ -29162,10 +29162,10 @@
         <v>0</v>
       </c>
       <c r="K370">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L370">
-        <v>0.20905853994181761</v>
+        <v>0.22037760483842214</v>
       </c>
     </row>
     <row r="371" spans="2:12" x14ac:dyDescent="0.45">
@@ -29179,28 +29179,28 @@
         <v>295</v>
       </c>
       <c r="E371">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="F371">
-        <v>0.46879999999999988</v>
+        <v>2.0799999999999999E-2</v>
       </c>
       <c r="G371">
         <v>1</v>
       </c>
       <c r="H371">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I371">
-        <v>21.450000000000006</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J371">
         <v>0</v>
       </c>
       <c r="K371">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L371">
-        <v>0.20645573625516284</v>
+        <v>0.22057989228923436</v>
       </c>
     </row>
     <row r="372" spans="2:12" x14ac:dyDescent="0.45">
@@ -29214,28 +29214,28 @@
         <v>295</v>
       </c>
       <c r="E372">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="F372">
-        <v>7.0000000000000007E-2</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="G372">
         <v>1</v>
       </c>
       <c r="H372">
-        <v>1138.5</v>
+        <v>1336.5</v>
       </c>
       <c r="I372">
-        <v>18.150000000000002</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J372">
         <v>0</v>
       </c>
       <c r="K372">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L372">
-        <v>0.2138278512842284</v>
+        <v>0.21997659078087359</v>
       </c>
     </row>
     <row r="373" spans="2:12" x14ac:dyDescent="0.45">
@@ -29249,115 +29249,115 @@
         <v>295</v>
       </c>
       <c r="E373">
-        <v>2025</v>
+        <v>2015</v>
       </c>
       <c r="F373">
-        <v>0.105</v>
+        <v>0.25670000000000009</v>
       </c>
       <c r="G373">
         <v>1</v>
       </c>
       <c r="H373">
-        <v>1223.3571428571429</v>
+        <v>1336.4999999999993</v>
       </c>
       <c r="I373">
-        <v>19.56428571428572</v>
+        <v>21.45</v>
       </c>
       <c r="J373">
         <v>0</v>
       </c>
       <c r="K373">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L373">
-        <v>0.2115734559696158</v>
+        <v>0.22051250081948157</v>
       </c>
     </row>
     <row r="374" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B374" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C374" t="s">
         <v>252</v>
       </c>
       <c r="D374" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E374">
-        <v>2028</v>
+        <v>2015</v>
       </c>
       <c r="F374">
-        <v>7.1999999999999995E-2</v>
+        <v>0.13950000000000004</v>
       </c>
       <c r="G374">
         <v>1</v>
       </c>
       <c r="H374">
-        <v>1336.5</v>
+        <v>1336.4999999999998</v>
       </c>
       <c r="I374">
-        <v>21.450000000000003</v>
+        <v>21.450000000000006</v>
       </c>
       <c r="J374">
         <v>0</v>
       </c>
       <c r="K374">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L374">
-        <v>0.20576891319722002</v>
+        <v>0.22263780528731941</v>
       </c>
     </row>
     <row r="375" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B375" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C375" t="s">
         <v>252</v>
       </c>
       <c r="D375" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E375">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="F375">
-        <v>7.5999999999999998E-2</v>
+        <v>0.14520000000000005</v>
       </c>
       <c r="G375">
         <v>1</v>
       </c>
       <c r="H375">
-        <v>1154.1315789473683</v>
+        <v>1336.4999999999995</v>
       </c>
       <c r="I375">
-        <v>18.410526315789479</v>
+        <v>21.45</v>
       </c>
       <c r="J375">
         <v>0</v>
       </c>
       <c r="K375">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L375">
-        <v>0.18367495595626879</v>
+        <v>0.20450924525813621</v>
       </c>
     </row>
     <row r="376" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B376" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C376" t="s">
         <v>252</v>
       </c>
       <c r="D376" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E376">
         <v>2011</v>
       </c>
       <c r="F376">
-        <v>4.8000000000000001E-2</v>
+        <v>3.78E-2</v>
       </c>
       <c r="G376">
         <v>1</v>
@@ -29366,7 +29366,7 @@
         <v>1336.5</v>
       </c>
       <c r="I376">
-        <v>21.450000000000003</v>
+        <v>21.450000000000006</v>
       </c>
       <c r="J376">
         <v>0</v>
@@ -29375,59 +29375,59 @@
         <v>44</v>
       </c>
       <c r="L376">
-        <v>0.1830157785160744</v>
+        <v>0.21133391274598409</v>
       </c>
     </row>
     <row r="377" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B377" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C377" t="s">
         <v>252</v>
       </c>
       <c r="D377" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E377">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="F377">
-        <v>0.32480000000000003</v>
+        <v>0.03</v>
       </c>
       <c r="G377">
         <v>1</v>
       </c>
       <c r="H377">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I377">
-        <v>21.449999999999989</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J377">
         <v>0</v>
       </c>
       <c r="K377">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L377">
-        <v>0.18637364754073979</v>
+        <v>0.21706938938321105</v>
       </c>
     </row>
     <row r="378" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B378" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C378" t="s">
         <v>252</v>
       </c>
       <c r="D378" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="E378">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="F378">
-        <v>1.7000000000000001E-2</v>
+        <v>0.19839999999999994</v>
       </c>
       <c r="G378">
         <v>1</v>
@@ -29436,51 +29436,51 @@
         <v>1336.5</v>
       </c>
       <c r="I378">
-        <v>21.450000000000003</v>
+        <v>21.45000000000001</v>
       </c>
       <c r="J378">
         <v>0</v>
       </c>
       <c r="K378">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L378">
-        <v>0.1830157785160744</v>
+        <v>0.2132472405399122</v>
       </c>
     </row>
     <row r="379" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B379" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C379" t="s">
         <v>252</v>
       </c>
       <c r="D379" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E379">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="F379">
-        <v>0.20560000000000006</v>
+        <v>0.189</v>
       </c>
       <c r="G379">
         <v>1</v>
       </c>
       <c r="H379">
-        <v>1336.4999999999998</v>
+        <v>1180.4047619047619</v>
       </c>
       <c r="I379">
-        <v>21.450000000000003</v>
+        <v>18.848412698412702</v>
       </c>
       <c r="J379">
         <v>0</v>
       </c>
       <c r="K379">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L379">
-        <v>0.19688949549367962</v>
+        <v>0.21045830299807192</v>
       </c>
     </row>
     <row r="380" spans="2:12" x14ac:dyDescent="0.45">
@@ -29494,10 +29494,10 @@
         <v>301</v>
       </c>
       <c r="E380">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="F380">
-        <v>1.0500000000000001E-2</v>
+        <v>1.9E-2</v>
       </c>
       <c r="G380">
         <v>1</v>
@@ -29512,10 +29512,10 @@
         <v>0</v>
       </c>
       <c r="K380">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="L380">
-        <v>0.19372001814840661</v>
+        <v>0.21831799184116799</v>
       </c>
     </row>
     <row r="381" spans="2:12" x14ac:dyDescent="0.45">
@@ -29529,28 +29529,28 @@
         <v>301</v>
       </c>
       <c r="E381">
-        <v>2015</v>
+        <v>2028</v>
       </c>
       <c r="F381">
-        <v>3.2699999999999993E-2</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="G381">
         <v>1</v>
       </c>
       <c r="H381">
-        <v>1336.5000000000002</v>
+        <v>1336.5</v>
       </c>
       <c r="I381">
-        <v>21.450000000000006</v>
+        <v>21.450000000000003</v>
       </c>
       <c r="J381">
         <v>0</v>
       </c>
       <c r="K381">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L381">
-        <v>0.18489803177812383</v>
+        <v>0.21892389070522661</v>
       </c>
     </row>
     <row r="382" spans="2:12" x14ac:dyDescent="0.45">
@@ -29561,7 +29561,7 @@
         <v>252</v>
       </c>
       <c r="D382" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E382">
         <v>2021</v>
@@ -29596,7 +29596,7 @@
         <v>252</v>
       </c>
       <c r="D383" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E383">
         <v>2028</v>
@@ -29631,7 +29631,7 @@
         <v>252</v>
       </c>
       <c r="D384" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="E384">
         <v>2010</v>
@@ -29666,7 +29666,7 @@
         <v>252</v>
       </c>
       <c r="D385" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="E385">
         <v>2028</v>
@@ -29701,7 +29701,7 @@
         <v>252</v>
       </c>
       <c r="D386" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="E386">
         <v>2014</v>

--- a/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
+++ b/VerveStacks_ITA/vt_vervestacks_ITA_v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D5BB9BA-6163-4C18-92E5-4E866503F15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8E2CECA-CB4B-4A25-B480-705FF3803FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5B0B6B3B-D97C-49FA-8746-1DDB9CBCE3CB}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{51B08040-6A90-43CE-A7B9-10FDFF8E5561}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -3439,7 +3439,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D5EC1D2-0122-4F42-854C-B7EB053F0709}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7484821-E64C-4595-91E9-8DE7B12F27B9}">
   <dimension ref="B9:T137"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9652,7 +9652,7 @@
         <v>874</v>
       </c>
       <c r="P120" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="Q120" t="s">
         <v>361</v>
@@ -9708,7 +9708,7 @@
         <v>874</v>
       </c>
       <c r="P121" t="s">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="Q121" t="s">
         <v>361</v>
@@ -10592,7 +10592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5738227A-1D00-4C7D-AD8E-261AF5D94122}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75A6EBC-48A4-45C6-95C0-E6EEAD10F3E6}">
   <dimension ref="B9:T98"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15513,7 +15513,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF3A32E-1900-40EE-8211-892817953584}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45F00382-A6F7-44CD-970D-CE88B9D467EB}">
   <dimension ref="B9:T527"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21749,7 +21749,7 @@
         <v>132</v>
       </c>
       <c r="P127" t="s">
-        <v>479</v>
+        <v>360</v>
       </c>
       <c r="Q127" t="s">
         <v>361</v>
@@ -21802,7 +21802,7 @@
         <v>132</v>
       </c>
       <c r="P128" t="s">
-        <v>360</v>
+        <v>479</v>
       </c>
       <c r="Q128" t="s">
         <v>361</v>
@@ -29103,7 +29103,7 @@
         <v>290</v>
       </c>
       <c r="P267" t="s">
-        <v>360</v>
+        <v>479</v>
       </c>
       <c r="Q267" t="s">
         <v>361</v>
@@ -29156,7 +29156,7 @@
         <v>290</v>
       </c>
       <c r="P268" t="s">
-        <v>479</v>
+        <v>360</v>
       </c>
       <c r="Q268" t="s">
         <v>361</v>
@@ -29739,7 +29739,7 @@
         <v>307</v>
       </c>
       <c r="P279" t="s">
-        <v>360</v>
+        <v>479</v>
       </c>
       <c r="Q279" t="s">
         <v>361</v>
@@ -29792,7 +29792,7 @@
         <v>307</v>
       </c>
       <c r="P280" t="s">
-        <v>479</v>
+        <v>360</v>
       </c>
       <c r="Q280" t="s">
         <v>361</v>
@@ -29845,7 +29845,7 @@
         <v>308</v>
       </c>
       <c r="P281" t="s">
-        <v>479</v>
+        <v>360</v>
       </c>
       <c r="Q281" t="s">
         <v>361</v>
@@ -29898,7 +29898,7 @@
         <v>308</v>
       </c>
       <c r="P282" t="s">
-        <v>360</v>
+        <v>479</v>
       </c>
       <c r="Q282" t="s">
         <v>361</v>
@@ -30640,7 +30640,7 @@
         <v>335</v>
       </c>
       <c r="P296" t="s">
-        <v>479</v>
+        <v>360</v>
       </c>
       <c r="Q296" t="s">
         <v>361</v>
@@ -30693,7 +30693,7 @@
         <v>335</v>
       </c>
       <c r="P297" t="s">
-        <v>360</v>
+        <v>479</v>
       </c>
       <c r="Q297" t="s">
         <v>361</v>
@@ -31453,7 +31453,7 @@
         <v>33</v>
       </c>
       <c r="L314">
-        <v>0.20827624154866117</v>
+        <v>0.20827624154866123</v>
       </c>
     </row>
     <row r="315" spans="2:20" x14ac:dyDescent="0.45">
@@ -31479,7 +31479,7 @@
         <v>33</v>
       </c>
       <c r="L315">
-        <v>0.20827624154866117</v>
+        <v>0.20827624154866123</v>
       </c>
     </row>
     <row r="316" spans="2:20" x14ac:dyDescent="0.45">
@@ -31505,7 +31505,7 @@
         <v>33</v>
       </c>
       <c r="L316">
-        <v>0.20827624154866117</v>
+        <v>0.20827624154866123</v>
       </c>
     </row>
     <row r="317" spans="2:20" x14ac:dyDescent="0.45">
@@ -38872,7 +38872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25E5B424-44B9-4964-895A-AA918E72A37A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BAD738C-41BF-4E36-82BB-FD16BEF0B385}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
